--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$J$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="64" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -509,7 +509,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（30ケース）。上から順に実施する。S-01〜S-06が準備、T-01以降が検証。T-24は動作テストでは検出できない境界設計を実装物で確認する設計レビュー。黄色は記入欄。</t>
+          <t>確かめる手順。上から順に実施する。S-01〜S-06が準備、T-01以降が検証。T-24は動作テストでは検出できない境界設計を実装物で確認する設計レビュー。黄色は記入欄。</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>dataset/08 のとおり作成（経理担当・人事担当・エリア長・バイトリーダー・閲覧のみ・スタッフ）。**エリア長は既定テンプレートに無い＝店長を雛形に選び、権限名を『検証_エリア長』に変えて作る**（顧客が実際に行うカスタマイズの再現）。保存後に再度開いて設定が再現するか確認</t>
+          <t>dataset/08 のとおり作成（経理担当（会社）・経理担当（店舗）・人事担当・エリア長・バイトリーダー・閲覧のみ・スタッフ の7権限）。**エリア長は既定テンプレートに無い＝店長を雛形に選び、権限名を『検証_エリア長』に変えて作る**（顧客が実際に行うカスタマイズの再現）。保存後に再度開いて設定が再現するか確認</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>6権限が保存でき、欠落・反転が0件</t>
+          <t>7権限が保存でき、欠落・反転が0件</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -764,12 +764,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>dataset/07 のとおり割当（US-03=渋谷・新宿、US-04/06=渋谷、US-07=新宿）</t>
+          <t>dataset/07 のとおり割当（US-01=経理（会社）／US-08=経理（店舗）全店／US-03=渋谷・新宿／US-04・US-06=渋谷／US-07は付け替え用）</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>全員に割当が保存され、店舗の権限に担当店舗が付く。1人に2つ以上は選べない</t>
+          <t>全員に割当が保存され、店舗の権限に担当店舗が付く。会社の権限には担当店舗の欄が出ない。1人に2つ以上は選べない</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>US-01 経理</t>
+          <t>US-01 経理（会社）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>US-01 経理でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
+          <t>US-01（経理・区分=会社）でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>【できる】売上分析・仕入分析・詳細分析・集計・お支払い・費用設定・予算設定の7画面が開ける 【できない】従業員管理・従業員（閲覧）・権限設定がメニューに出ず、直URLでも開けない</t>
+          <t>【できる】売上分析・仕入分析・詳細分析・集計・お支払いの5画面が開ける 【できない】従業員管理・従業員（閲覧）・権限設定がメニューに出ず、直URLでも開けない。費用設定・予算設定は店舗画面のため会社スコープに存在しない</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>T-10</t>
+          <t>T-09b</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>US-02 人事</t>
+          <t>US-08 経理（店舗・全店）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1248,22 +1248,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>US-02 人事でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
+          <t>US-08（経理・区分=店舗／担当店舗=全店）でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>【できる】従業員（閲覧）・従業員管理・締め状況・締め管理の4画面が開ける 【できない】売上系4画面とお支払いが開けず、**ダッシュボードにも売上・利益が出ない**</t>
+          <t>【できる】売上分析・仕入分析・詳細分析・集計・費用設定・予算設定の6画面が開け、3店舗すべてのデータが見える 【できない】従業員管理・従業員（閲覧）・権限設定が開けない。お支払いは会社画面のため店舗スコープに存在しない</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>T-10</t>
+          <t>T-09b</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>AC-10 AC-11／F-11</t>
+          <t>AC-10 AC-11 AC-16／F-11</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr"/>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>T-11</t>
+          <t>T-10</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>US-03 エリア長（店長ベースのカスタマイズ例）</t>
+          <t>US-02 人事</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1292,22 +1292,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>US-03 検証_エリア長でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
+          <t>US-02 人事でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>【できる】渋谷店・新宿店が見え、切替に2店舗が並ぶ。集計の合計＝3,000,000 【できない】池袋店が切替に出ず合計に含まれない（**7,000,000なら混入＝NG**）。池袋の従業員（給与80万）も見えない</t>
+          <t>【できる】従業員（閲覧）・従業員管理・締め状況・締め管理の4画面が開ける 【できない】売上系4画面とお支払いが開けず、**ダッシュボードにも売上・利益が出ない**</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>T-11</t>
+          <t>T-10</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>AC-10 AC-11 AC-23／F-14</t>
+          <t>AC-10 AC-11／F-11</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr"/>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>T-12</t>
+          <t>T-11</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>US-04 バイトL</t>
+          <t>US-03 エリア長（店長ベースのカスタマイズ例）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1336,22 +1336,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>US-04 バイトLでログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
+          <t>US-03 検証_エリア長でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>【できる】売上分析が開け渋谷店の売上が見える 【できない】6画面が開けず、売上分析の中に原価率・粗利・人件費率が出ない</t>
+          <t>【できる】渋谷店・新宿店が見え、切替に2店舗が並ぶ。集計の合計＝3,000,000 【できない】池袋店が切替に出ず合計に含まれない（**7,000,000なら混入＝NG**）。池袋の従業員（給与80万）も見えない</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>T-12</t>
+          <t>T-11</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>AC-10 AC-11／F-11</t>
+          <t>AC-10 AC-11 AC-23／F-14</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr"/>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>T-13</t>
+          <t>T-12</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>US-05 閲覧のみ</t>
+          <t>US-04 バイトL</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1380,17 +1380,17 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>US-05 閲覧のみでログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
+          <t>US-04 バイトLでログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>【できる】全画面が開ける 【できない】（更新できてしまうかはT-23で記録）</t>
+          <t>【できる】売上分析が開け渋谷店の売上が見える 【できない】6画面が開けず、売上分析の中に原価率・粗利・人件費率が出ない</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>T-13</t>
+          <t>T-12</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>T-14</t>
+          <t>T-13</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>US-06 スタッフ</t>
+          <t>US-05 閲覧のみ</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1424,66 +1424,66 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>US-06 スタッフでログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
+          <t>US-05 閲覧のみでログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>【できる】ダッシュボードに着地し、開ける画面は1つだけ 【できない】他の画面を直URLで開いても全てブロック。空白・エラー・ループにならない</t>
+          <t>【できる】会社スコープの全21画面が開ける 【できない】（更新できてしまうかはT-23で記録）。費用設定など店舗専用画面は会社スコープに存在しない</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>T-14</t>
+          <t>T-13</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>AC-10 AC-11 AC-13／F-11</t>
+          <t>AC-10 AC-11／F-11</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr"/>
       <c r="J22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>割当</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>T-15</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>権限の付け替えと置き換えの明示</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>権限が効くか</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>T-14</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>US-06 スタッフ</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>US-07（検証_エリア長）の割当編集で経理担当に付け替え、行の表示を確認してから保存→US-07でログイン。次に一括割当で同じ人を含める</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>付け替え前に「選ぶと『◯◯』から置き換わります」。保存後は経理の画面だけが開き、エリア長固有の画面は開けない。一括割当に「⚠既に『◯◯』を保持。含めると置き換わります」「✓この権限で登録済み」＋保存前の確認</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>T-15</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>AC-14 AC-15／F-05 F-10 F-13 F-23</t>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>US-06 スタッフでログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>【できる】ダッシュボードに着地し、開ける画面は1つだけ 【できない】他の画面を直URLで開いても全てブロック。空白・エラー・ループにならない</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>T-14</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>AC-10 AC-11 AC-13／F-11</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr"/>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>T-16</t>
+          <t>T-15</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>区分フィルタ</t>
+          <t>権限の付け替えと置き換えの明示</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1512,22 +1512,22 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>検証_エリア長（店舗）で一括割当を開く→「すべて表示」</t>
+          <t>US-07（検証_エリア長・店舗）の割当編集で 検証_経理担当（会社）に付け替え、行の表示を確認してから保存→US-07でログイン</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>既定では店舗所属者のみ。すべて表示で全員が出る</t>
+          <t>付け替え前に「選ぶと『検証_エリア長』から置き換わります」が行に表示。保存後は経理（会社）の画面だけが開き、エリア長固有の店舗画面は開けない。**担当店舗の欄が消え全社になる**</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>T-16</t>
+          <t>T-15</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>AC-15／F-10</t>
+          <t>AC-14 AC-15／F-05 F-10 F-13 F-23</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr"/>
@@ -1541,37 +1541,37 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>T-17</t>
+          <t>T-16</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>締め出しと越権の防止</t>
+          <t>区分フィルタ</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>S-01 S-05</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>自ロールから権限設定をなしにして保存を試みる。次にUS-04（店舗）で権限設定のURLを直接開く</t>
+          <t>検証_エリア長（店舗）で一括割当を開く→「すべて表示」</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>警告が出るか最後の全権は外せない。一般の権限では権限設定が開けない</t>
+          <t>既定では店舗所属者のみ。すべて表示で全員が出る</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>T-17</t>
+          <t>T-16</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>AC-17 AC-18／F-24</t>
+          <t>AC-15／F-10</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr"/>
@@ -1585,81 +1585,81 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>T-18</t>
+          <t>T-17</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>権限を外す・店舗未紐付け</t>
+          <t>締め出しと越権の防止</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-01 S-05</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>US-06の割当編集で「割当なし」を選び保存→ログイン確認→S-05に戻す。次に店舗を選ばず店舗の権限を割当して保存</t>
+          <t>自ロールから権限設定をなしにして保存を試みる。次にUS-04（店舗）で権限設定のURLを直接開く</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>未割当になり画面が出ない。店舗0件はエラーまたは警告</t>
+          <t>警告が出るか最後の全権は外せない。一般の権限では権限設定が開けない</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>T-18</t>
+          <t>T-17</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>AC-04 AC-19／F-14 F-15</t>
+          <t>AC-17 AC-18／F-24</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr"/>
       <c r="J26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>指標</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>T-19</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>指標一覧と既定件数</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>割当</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>T-18</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>権限を外す・店舗未紐付け</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>スタッフ・検証_エリア長・経理の指標一覧を開き、店舗／会社タブのON件数を数える。任意の指標をON/OFF</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>スタッフ=店舗17/会社0、エリア長（店長ベース）=店舗36/会社8、経理=店舗36/会社25。切替は即時反映</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>T-19</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>AC-25／F-16</t>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>US-06の割当編集で「割当なし」を選び保存→ログイン確認→S-05に戻す。次に店舗を選ばず店舗の権限を割当して保存</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>未割当になり画面が出ない。店舗0件はエラーまたは警告</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>T-18</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>AC-04 AC-19／F-14 F-15</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr"/>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-19</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>一括設定・再利用・オーナー専用</t>
+          <t>指標一覧と既定件数</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1688,209 +1688,253 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>指標条件設定で推奨テンプレ「店長向け」を適用（キャンセルとの差も確認）→マイテンプレートに保存→別の権限で読込。次に「👑オーナー操作」の指標管理と付与先指定</t>
+          <t>スタッフ・検証_エリア長・経理の指標一覧を開き、店舗／会社タブのON件数を数える。任意の指標をON/OFF</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>適用後=店舗36/会社8。キャンセルでは反映されない。保存した組み合わせがマイテンプレートに登録され他権限で読込できる。指標管理は全件表示で編集UIが出ない</t>
+          <t>スタッフ=店舗17/会社0、エリア長（店長ベース）=店舗36/会社8、経理=店舗36/会社25。切替は即時反映</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-19</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>AC-29 AC-30／F-17 F-18 F-19 F-20</t>
+          <t>AC-25／F-16</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr"/>
       <c r="J28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>移植</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>T-21</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>現行3権限の移植と漏れ</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>S-06</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>プリセット適用後に master／manager／shop_manager で全メニューを再取得しS-06と突合。ユーザー割当一覧で未割当を数える</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>3権限とも見える画面が完全一致（増減0）。ロール未割当＝0名</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>T-21×3</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>AC-01 AC-02 AC-03 AC-04</t>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>指標</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>T-20</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>一括設定・再利用・オーナー専用</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>S-05</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>指標条件設定で推奨テンプレ「店長向け」を適用（キャンセルとの差も確認）→マイテンプレートに保存→別の権限で読込。次に「👑オーナー操作」の指標管理と付与先指定</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>適用後=店舗36/会社8。キャンセルでは反映されない。保存した組み合わせがマイテンプレートに登録され他権限で読込できる。指標管理は全件表示で編集UIが出ない</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>T-20</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>AC-29 AC-30／F-17 F-18 F-19 F-20</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr"/>
       <c r="J29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>設計レビュー</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>T-24</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>境界設計の確認（動作テストでは検出できない）</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>S-01</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>エンジニアと画面・APIを一緒に棚卸しし、6点を確認する。①ユーザー個別に権限内容を編集できるUI/APIが無いか ②店舗ロールでも担当店舗を全店・複数店に設定できるか ③権限の状態が なし/閲覧/操作 の3つだけか ④指標一覧に機密度のバッジが出ていないか ⑤店舗ロールの指標一覧で会社指標をONにできるか（既定OFF）⑥一括割当で店舗を選んだだけでは権限が付与されないか</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>6点すべてが設計どおり。**動くかどうかではなく「そう作られているか」を見る**。1つでも崩れていると、画面は正常に動くのに後から権限が破綻する</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>T-24_レビュー記録</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>AC-K01〜K06／F-11 F-14 F-16 F-22</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>移植</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>T-21</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>現行3権限の移植と漏れ</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>S-06</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>プリセット適用後に master／manager／shop_manager で全メニューを再取得しS-06と突合。ユーザー割当一覧で未割当を数える</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>3権限とも見える画面が完全一致（増減0）。ロール未割当＝0名</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>T-21×3</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>AC-01 AC-02 AC-03 AC-04</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr"/>
       <c r="J30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>T-22</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>6シナリオの意図判定</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>T-09〜T-14 T-20</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>各シナリオが意図どおり作れたかを判定</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>6件を ◯作れる／△粒度不足／×作れない で記録。**【必須ライン】画面単位で表現できる SC-01経理・SC-02人事・SC-04バイトL・SC-06スタッフ の4件で ×＝0件**（AC-22）。SC-03エリア長・SC-05閲覧のみ はデータ範囲・操作を要するため P1 では×が想定され、それが P2/P3 を前倒しする根拠になる（AC-32）</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>AC-22 AC-32</t>
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>設計レビュー</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>T-24</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>境界設計の確認（動作テストでは検出できない）</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>S-01</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>エンジニアと画面・APIを一緒に棚卸しし、6点を確認する。①ユーザー個別に権限内容を編集できるUI/APIが無いか ②店舗ロールでも担当店舗を全店・複数店に設定できるか ③権限の状態が なし/閲覧/操作 の3つだけか ④指標一覧に機密度のバッジが出ていないか ⑤店舗ロールの指標一覧で会社指標をONにできるか（既定OFF）⑥一括割当で店舗を選んだだけでは権限が付与されないか</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>6点すべてが設計どおり。**動くかどうかではなく「そう作られているか」を見る**。1つでも崩れていると、画面は正常に動くのに後から権限が破綻する</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>T-24_レビュー記録</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>AC-K01〜K06／F-11 F-14 F-16 F-22</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr"/>
       <c r="J31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>T-22</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>6シナリオの意図判定</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>T-09〜T-14 T-20</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>各シナリオが意図どおり作れたかを判定</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>6件を ◯作れる／△粒度不足／×作れない で記録。**【必須ライン】画面単位で表現できる SC-01経理・SC-02人事・SC-04バイトL・SC-06スタッフ の4件で ×＝0件**（AC-22）。SC-03エリア長・SC-05閲覧のみ はデータ範囲・操作を要するため P1 では×が想定され、それが P2/P3 を前倒しする根拠になる（AC-32）</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>AC-22 AC-32</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>T-23</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>対象外4項目の実測</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>S-05 T-11</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>①US-05で費用設定の金額を変更し保存（値が更新されるか）②T-11の合計が3,000,000だったか ③US-02のダッシュボード等に出る指標を数える ④権限の作成・割当の操作ログを確認</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>①US-05（閲覧のみ・区分=会社）で会社情報を変更し保存（値が更新されるか）②T-11の合計が3,000,000だったか ③US-02のダッシュボード等に出る指標を数える ④権限の作成・割当の操作ログを確認</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>判定せず実測のみ記録。①更新できる→P2が必要 ②7,000,000→P3が必要 ③許可外の指標が出る→P4が必要 ④ログが無い→P5が必要</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>T-23</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>AC-23 AC-24 AC-25 AC-26</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr"/>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J32"/>
+  <autoFilter ref="A2:J33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$J$33</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -28,9 +26,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="001F4E5F"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -38,7 +36,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -47,32 +45,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E5F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F7FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF9E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDECEA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF4E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
+        <fgColor rgb="001F7A8C"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,50 +59,51 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D6DEE5"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D6DEE5"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D6DEE5"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D6DEE5"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D8F0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FBDCDC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -494,26 +468,26 @@
   <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="64" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順。上から順に実施する。S-01〜S-06が準備、T-01以降が検証。T-24は動作テストでは検出できない境界設計を実装物で確認する設計レビュー。黄色は記入欄。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
+          <t>確かめる手順。上から順に実施する。S-01〜S-06 は準備、T-01〜 が検証。「判定」に OK / NG を入れる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>段階</t>
@@ -565,7 +539,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="88" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -606,10 +580,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="88" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -650,10 +624,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="88" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -694,10 +668,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="88" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -738,10 +712,10 @@
           <t>AC-07／F-03</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="88" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -782,10 +756,10 @@
           <t>AC-14 AC-16／F-11 F-14</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="88" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -826,186 +800,186 @@
           <t>AC-01〜03</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>設定</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>T-01</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>基本情報・雛形・デモモード</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>新規作成を開き入力項目を記録。雛形（ベース）の候補を確認。ヘッダーで新規導入デモ／運用デモを切り替える</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>項目名を記録（仕様=権限名/区分、実装=キー/ロール名/種別）。雛形に移植プリセットが出る。運用デモでは「既存権限をコピー」が増える</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>T-01</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>AC-08／F-03 F-26</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>設定</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>T-02</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>初期値と既定の安全側</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>雛形＝新規作成（プレーン）を選び許可数を確認。既存と同じキーで保存、キー空欄でも保存。新規画面追加時の既定値をエンジニアに確認</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>プレーンは許可0件。キー重複はエラー。新規画面の既定＝なし（fail-closed）</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>T-02</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>AC-09 AC-12</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr"/>
-      <c r="J10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>設定</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>T-03</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>区分の出し分けと画面数</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>新規作成で区分を会社→店舗に切替。それぞれ全展開してカテゴリ数を数える</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>会社=21（会社情報/お支払い/店舗管理/ダウンロードが出る）、店舗=23（発注先&amp;仕入商品/店舗情報/連携設定/費用設定/休業日設定/予算設定が出る）。総数27カテゴリ53機能</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>T-03</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>AC-05 AC-06／F-21</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>設定</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>権限テンプレートの保存と破棄</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>権限テンプレート画面で選択途中に「一時保存」→離れて再訪→次に「下書きを破棄」→「適用」</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>保存した選択が復元される。破棄で既定に戻る。適用で権限一覧に登録される</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>AC-33／F-01 F-02 F-25</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr"/>
-      <c r="J12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="88" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>一覧・遷移</t>
@@ -1046,10 +1020,10 @@
           <t>AC-20 AC-31／F-22</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="88" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>一覧・遷移</t>
@@ -1090,10 +1064,10 @@
           <t>AC-28／F-12</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="88" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>一覧・遷移</t>
@@ -1134,10 +1108,10 @@
           <t>AC-27／F-04 F-06 F-07 F-08 F-09</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="88" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>一覧・遷移</t>
@@ -1178,318 +1152,318 @@
           <t>AC-21／F-06</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr"/>
-      <c r="J16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>権限が効くか</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>T-09</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>US-01 経理（会社）</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>US-01（経理・区分=会社）でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>【できる】売上分析・仕入分析・詳細分析・集計・お支払いの5画面が開ける 【できない】従業員管理・従業員（閲覧）・権限設定がメニューに出ず、直URLでも開けない。費用設定・予算設定は店舗画面のため会社スコープに存在しない</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>T-09</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>AC-10 AC-11／F-11</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr"/>
-      <c r="J17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>権限が効くか</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>T-09b</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>US-08 経理（店舗・全店）</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>US-08（経理・区分=店舗／担当店舗=全店）でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>【できる】売上分析・仕入分析・詳細分析・集計・費用設定・予算設定の6画面が開け、3店舗すべてのデータが見える 【できない】従業員管理・従業員（閲覧）・権限設定が開けない。お支払いは会社画面のため店舗スコープに存在しない</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>T-09b</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>AC-10 AC-11 AC-16／F-11</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>権限が効くか</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>T-10</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>US-02 人事</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>US-02 人事でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>【できる】従業員（閲覧）・従業員管理・締め状況・締め管理の4画面が開ける 【できない】売上系4画面とお支払いが開けず、**ダッシュボードにも売上・利益が出ない**</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>T-10</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>AC-10 AC-11／F-11</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>権限が効くか</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>T-11</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>US-03 エリア長（店長ベースのカスタマイズ例）</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>US-03 検証_エリア長でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>【できる】渋谷店・新宿店が見え、切替に2店舗が並ぶ。集計の合計＝3,000,000 【できない】池袋店が切替に出ず合計に含まれない（**7,000,000なら混入＝NG**）。池袋の従業員（給与80万）も見えない</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>T-11</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>AC-10 AC-11 AC-23／F-14</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>権限が効くか</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>T-12</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>US-04 バイトL</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>US-04 バイトLでログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>【できる】売上分析が開け渋谷店の売上が見える 【できない】6画面が開けず、売上分析の中に原価率・粗利・人件費率が出ない</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>T-12</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>AC-10 AC-11／F-11</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>権限が効くか</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>T-13</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>US-05 閲覧のみ</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>US-05 閲覧のみでログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>【できる】会社スコープの全21画面が開ける 【できない】（更新できてしまうかはT-23で記録）。費用設定など店舗専用画面は会社スコープに存在しない</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>T-13</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>AC-10 AC-11／F-11</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr"/>
-      <c r="J22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>権限が効くか</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>T-14</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>US-06 スタッフ</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>US-06 スタッフでログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>【できる】ダッシュボードに着地し、開ける画面は1つだけ 【できない】他の画面を直URLで開いても全てブロック。空白・エラー・ループにならない</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>T-14</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>AC-10 AC-11 AC-13／F-11</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr"/>
-      <c r="J23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="88" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>割当</t>
@@ -1530,10 +1504,10 @@
           <t>AC-14 AC-15／F-05 F-10 F-13 F-23</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr"/>
-      <c r="J24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="88" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>割当</t>
@@ -1574,10 +1548,10 @@
           <t>AC-15／F-10</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr"/>
-      <c r="J25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="88" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t>割当</t>
@@ -1618,10 +1592,10 @@
           <t>AC-17 AC-18／F-24</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr"/>
-      <c r="J26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="88" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>割当</t>
@@ -1662,98 +1636,98 @@
           <t>AC-04 AC-19／F-14 F-15</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr"/>
-      <c r="J27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>T-19</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>指標一覧と既定件数</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>スタッフ・検証_エリア長・経理の指標一覧を開き、店舗／会社タブのON件数を数える。任意の指標をON/OFF</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>スタッフ=店舗17/会社0、エリア長（店長ベース）=店舗36/会社8、経理=店舗36/会社25。切替は即時反映</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>T-19</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>AC-25／F-16</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr"/>
-      <c r="J28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>T-20</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>一括設定・再利用・オーナー専用</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>指標条件設定で推奨テンプレ「店長向け」を適用（キャンセルとの差も確認）→マイテンプレートに保存→別の権限で読込。次に「👑オーナー操作」の指標管理と付与先指定</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>適用後=店舗36/会社8。キャンセルでは反映されない。保存した組み合わせがマイテンプレートに登録され他権限で読込できる。指標管理は全件表示で編集UIが出ない</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>T-20</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>AC-29 AC-30／F-17 F-18 F-19 F-20</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr"/>
-      <c r="J29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30">
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="88" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>移植</t>
@@ -1794,147 +1768,159 @@
           <t>AC-01 AC-02 AC-03 AC-04</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr"/>
-      <c r="J30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>設計レビュー</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>境界設計の確認（動作テストでは検出できない）</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>エンジニアと画面・APIを一緒に棚卸しし、6点を確認する。①ユーザー個別に権限内容を編集できるUI/APIが無いか ②店舗ロールでも担当店舗を全店・複数店に設定できるか ③権限の状態が なし/閲覧/操作 の3つだけか ④指標一覧に機密度のバッジが出ていないか ⑤店舗ロールの指標一覧で会社指標をONにできるか（既定OFF）⑥一括割当で店舗を選んだだけでは権限が付与されないか</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>6点すべてが設計どおり。**動くかどうかではなく「そう作られているか」を見る**。1つでも崩れていると、画面は正常に動くのに後から権限が破綻する</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>エンジニアと画面・APIを一緒に棚卸しし、7点を確認する。①ユーザー個別に権限内容を編集できるUI/APIが無いか ②店舗ロールでも担当店舗を全店・複数店に設定できるか ③権限の状態が なし/閲覧/操作 の3つだけか ④指標一覧に機密度のバッジが出ていないか ⑤店舗ロールの指標一覧で会社指標をONにできるか（既定OFF）⑥一括割当で店舗を選んだだけでは権限が付与されないか ⑦画面カテゴリを新しく追加したとき、既存の全権限で既定が「なし」になるか（コード上の既定値を確認）</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>7点すべてが設計どおり。**動くかどうかではなく「そう作られているか」を見る**。1つでも崩れていると、画面は正常に動くのに後から権限が破綻する</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>T-24_レビュー記録</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>AC-K01〜K06／F-11 F-14 F-16 F-22</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr"/>
-      <c r="J31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>K-01 K-02 K-03 K-04 K-05 K-06 K-07／F-11 F-14 F-16 F-22</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>T-22</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>6シナリオの意図判定</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>T-09〜T-14 T-20</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>各シナリオが意図どおり作れたかを判定</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>6件を ◯作れる／△粒度不足／×作れない で記録。**【必須ライン】画面単位で表現できる SC-01経理・SC-02人事・SC-04バイトL・SC-06スタッフ の4件で ×＝0件**（AC-22）。SC-03エリア長・SC-05閲覧のみ はデータ範囲・操作を要するため P1 では×が想定され、それが P2/P3 を前倒しする根拠になる（AC-32）</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>AC-22 AC-32</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr"/>
-      <c r="J32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>T-23</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>対象外4項目の実測</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>S-05 T-11</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>①US-05（閲覧のみ・区分=会社）で会社情報を変更し保存（値が更新されるか）②T-11の合計が3,000,000だったか ③US-02のダッシュボード等に出る指標を数える ④権限の作成・割当の操作ログを確認</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>判定せず実測のみ記録。①更新できる→P2が必要 ②7,000,000→P3が必要 ③許可外の指標が出る→P4が必要 ④ログが無い→P5が必要</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>T-23</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>AC-23 AC-24 AC-25 AC-26</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr"/>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J33"/>
+  <conditionalFormatting sqref="J3:J33">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"NG"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="J3:J33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"OK,NG,検証不能"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -1667,7 +1667,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>スタッフ=店舗17/会社0、エリア長（店長ベース）=店舗36/会社8、経理=店舗36/会社25。切替は即時反映</t>
+          <t>指標の既定ONは**雛形で決まる**。従業員ベース（スタッフ）=店舗17/会社0、店長ベース（エリア長・バイトリーダー・経理（店舗））=店舗36/会社8、本部管理ベース（経理（会社）・人事・閲覧のみ）=店舗36/会社25。**7権限すべてを dataset/09 の値と突合する**。切替は即時反映（保存ボタンなし）</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">

--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>経理=閲覧4/7・設定3／人事=閲覧2/7／バイトL=閲覧1/7／閲覧のみ=閲覧7/7・設定14。列選択が次回も保持（スコープ別）</t>
+          <t>**7権限すべてで**一覧の許可数＝実際の設定（不一致0件）。数値例＝経理(会社)=閲覧4/7・設定3／人事=閲覧2/7／バイトL=閲覧1/7／閲覧のみ=閲覧7/7・設定14。列選択が次回も保持（スコープ別）</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>6権限すべてで N＝実保持者数。保持者だけに絞り込まれバナーが出る</t>
+          <t>**7権限すべてで** N＝実保持者数。保持者だけに絞り込まれバナーが出る</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>エンジニアと画面・APIを一緒に棚卸しし、7点を確認する。①ユーザー個別に権限内容を編集できるUI/APIが無いか ②店舗ロールでも担当店舗を全店・複数店に設定できるか ③権限の状態が なし/閲覧/操作 の3つだけか ④指標一覧に機密度のバッジが出ていないか ⑤店舗ロールの指標一覧で会社指標をONにできるか（既定OFF）⑥一括割当で店舗を選んだだけでは権限が付与されないか ⑦画面カテゴリを新しく追加したとき、既存の全権限で既定が「なし」になるか（コード上の既定値を確認）</t>
+          <t>エンジニアと画面・APIを一緒に棚卸しし、7点を確認する。①ユーザー個別に権限内容を編集できるUI/APIが無いか ②店舗ロールでも担当店舗を全店・複数店に設定できるか ③権限の状態が なし/閲覧/操作 の3つだけか ④指標一覧に機密度のバッジが出ていないか ⑤店舗ロールの指標一覧で会社指標をONにできるか（既定OFF）⑥一括割当で店舗を選んだだけでは権限が付与されないか ⑦画面カテゴリを新しく追加したとき、既存の全権限で既定が「なし」になるか（AC-12 のコード上の既定値を確認）</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>K-01 K-02 K-03 K-04 K-05 K-06 K-07／F-11 F-14 F-16 F-22</t>
+          <t>K-01 K-02 K-03 K-04 K-05 K-06 AC-12／F-11 F-14 F-16 F-22</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr"/>

--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -831,7 +831,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>項目名を記録（仕様=権限名/区分、実装=キー/ロール名/種別）。雛形に移植プリセットが出る。運用デモでは「既存権限をコピー」が増える</t>
+          <t>項目名を記録（仕様=権限名/区分、実装=キー/ロール名/種別）。雛形に移植プリセットと「まっさら（なし）」が出る。運用デモでは「既存権限をコピー」が増える</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>雛形＝新規作成（プレーン）を選び許可数を確認。既存と同じキーで保存、キー空欄でも保存。新規画面追加時の既定値をエンジニアに確認</t>
+          <t>雛形＝「まっさら（なし）」を選び許可数を確認。既存と同じキーで保存、キー空欄でも保存。新規画面追加時の既定値をエンジニアに確認</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>プレーンは許可0件。キー重複はエラー。新規画面の既定＝なし（fail-closed）</t>
+          <t>「まっさら（なし）」は許可0件。キー重複はエラー。新規画面の既定＝なし（fail-closed）</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>4入口とも来た元に戻る。マス目からは該当箇所へ移動＋ハイライト。新規作成はベースがプレーン既定。**割当編集起点で「全員に反映される」警告があるか記録**</t>
+          <t>4入口とも来た元に戻る。マス目からは該当箇所へ移動＋ハイライト。新規作成はベースが「まっさら（なし）」既定。**割当編集起点で「全員に反映される」警告があるか記録**</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>6シナリオの意図判定</t>
+          <t>7シナリオの意図判定</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>6件を ◯作れる／△粒度不足／×作れない で記録。**【必須ライン】画面単位で表現できる SC-01経理・SC-02人事・SC-04バイトL・SC-06スタッフ の4件で ×＝0件**（AC-22）。SC-03エリア長・SC-05閲覧のみ はデータ範囲・操作を要するため P1 では×が想定され、それが P2/P3 を前倒しする根拠になる（AC-32）</t>
+          <t>7件を ◯作れる／△粒度不足／×作れない で記録。**【必須ライン】画面単位で表現できる SC-01a経理（会社）・SC-01b経理（店舗）・SC-02人事・SC-04バイトL・SC-06スタッフ の5件で ×＝0件**（AC-22）。SC-03エリア長・SC-05閲覧のみ はデータ範囲・操作を要するため P1 では×が想定され、それが P2/P3 を前倒しする根拠になる（AC-32・判定せず記録のみ）</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">

--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>5権限の一覧タブ／設定タブの内訳を数える。表示ロール・権限列設定を変更→離れて再訪</t>
+          <t>**7権限すべての**一覧タブ／設定タブの内訳を数える。表示ロール・権限列設定を変更→離れて再訪</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">

--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -465,19 +465,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="56" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,16 +531,21 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>ヘルプページの該当箇所</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>実際の値</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="88" customHeight="1">
+    <row r="3" ht="94" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -580,10 +586,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>—（環境確認）</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="88" customHeight="1">
+      <c r="K3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="94" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -624,10 +635,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>—（データ投入）</t>
+        </is>
+      </c>
       <c r="J4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5" ht="88" customHeight="1">
+      <c r="K4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="94" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -668,10 +684,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>—（ユーザーの登録）</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="88" customHeight="1">
+      <c r="K5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="94" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -712,10 +733,15 @@
           <t>AC-07／F-03</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>ケース別のやり方</t>
+        </is>
+      </c>
       <c r="J6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7" ht="88" customHeight="1">
+      <c r="K6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="94" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -756,10 +782,15 @@
           <t>AC-14 AC-16／F-11 F-14</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>権限をメンバーに割り当てる／担当店舗を設定する</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="88" customHeight="1">
+      <c r="K7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="94" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -800,10 +831,15 @@
           <t>AC-01〜03</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>—（移植前の記録）</t>
+        </is>
+      </c>
       <c r="J8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9" ht="88" customHeight="1">
+      <c r="K8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="94" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>設定</t>
@@ -844,10 +880,15 @@
           <t>AC-08／F-03 F-26</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>権限を作成する STEP 2　雛形を選ぶ／STEP 3　権限名と区分を決める</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" ht="88" customHeight="1">
+      <c r="K9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="94" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>設定</t>
@@ -888,10 +929,15 @@
           <t>AC-09 AC-12</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>権限を作成する STEP 2（まっさら（なし））／よくあるご質問（新しい画面が追加された場合）</t>
+        </is>
+      </c>
       <c r="J10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11" ht="88" customHeight="1">
+      <c r="K10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="94" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>設定</t>
@@ -932,10 +978,15 @@
           <t>AC-05 AC-06／F-21</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>権限を作成する STEP 3（図3 会社と店舗の区分）</t>
+        </is>
+      </c>
       <c r="J11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="88" customHeight="1">
+      <c r="K11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="94" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>設定</t>
@@ -976,10 +1027,15 @@
           <t>AC-33／F-01 F-02 F-25</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>導入時の初期設定</t>
+        </is>
+      </c>
       <c r="J12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13" ht="88" customHeight="1">
+      <c r="K12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="94" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>一覧・遷移</t>
@@ -1020,10 +1076,15 @@
           <t>AC-20 AC-31／F-22</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>設定内容を確認する（権限一覧）</t>
+        </is>
+      </c>
       <c r="J13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="88" customHeight="1">
+      <c r="K13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="94" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>一覧・遷移</t>
@@ -1064,10 +1125,15 @@
           <t>AC-28／F-12</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>設定内容を確認する（役割サマリ）／権限をメンバーに割り当てる 方法3</t>
+        </is>
+      </c>
       <c r="J14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15" ht="88" customHeight="1">
+      <c r="K14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="94" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>一覧・遷移</t>
@@ -1108,10 +1174,15 @@
           <t>AC-27／F-04 F-06 F-07 F-08 F-09</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>作成した権限を修正する（入口の一覧表）</t>
+        </is>
+      </c>
       <c r="J15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="88" customHeight="1">
+      <c r="K15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="94" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>一覧・遷移</t>
@@ -1152,10 +1223,15 @@
           <t>AC-21／F-06</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>よくあるご質問（設定した権限はいつから反映されますか）</t>
+        </is>
+      </c>
       <c r="J16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17" ht="88" customHeight="1">
+      <c r="K16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="94" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>権限が効くか</t>
@@ -1196,10 +1272,15 @@
           <t>AC-10 AC-11／F-11</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（経理担当に、売上とお支払だけ見せたい）</t>
+        </is>
+      </c>
       <c r="J17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="88" customHeight="1">
+      <c r="K17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="94" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>権限が効くか</t>
@@ -1240,10 +1321,15 @@
           <t>AC-10 AC-11 AC-16／F-11</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（経理担当に、売上とお支払だけ見せたい ＋ 会社と店舗の両方の画面を使わせたい）</t>
+        </is>
+      </c>
       <c r="J18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19" ht="88" customHeight="1">
+      <c r="K18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="94" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>権限が効くか</t>
@@ -1284,10 +1370,15 @@
           <t>AC-10 AC-11／F-11</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（人事担当に、従業員情報だけ見せたい）</t>
+        </is>
+      </c>
       <c r="J19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="88" customHeight="1">
+      <c r="K19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="94" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>権限が効くか</t>
@@ -1328,10 +1419,15 @@
           <t>AC-10 AC-11 AC-23／F-14</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（複数の店舗をまとめて見せたい）／担当店舗を設定する（図2）</t>
+        </is>
+      </c>
       <c r="J20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21" ht="88" customHeight="1">
+      <c r="K20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="94" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>権限が効くか</t>
@@ -1372,10 +1468,15 @@
           <t>AC-10 AC-11／F-11</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（アルバイトリーダーに、一部の画面だけ見せたい）</t>
+        </is>
+      </c>
       <c r="J21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="88" customHeight="1">
+      <c r="K21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="94" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>権限が効くか</t>
@@ -1416,10 +1517,15 @@
           <t>AC-10 AC-11／F-11</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>権限を作成する STEP 4（「閲覧」と「操作」は、今回のリリースではどちらも）</t>
+        </is>
+      </c>
       <c r="J22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23" ht="88" customHeight="1">
+      <c r="K22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="94" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
           <t>権限が効くか</t>
@@ -1460,10 +1566,15 @@
           <t>AC-10 AC-11 AC-13／F-11</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（新しく入った方には、まず最小限から始めたい）／よくあるご質問（権限を絞りすぎて、何も見えなくなりませんか）</t>
+        </is>
+      </c>
       <c r="J23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="88" customHeight="1">
+      <c r="K23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="94" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>割当</t>
@@ -1504,10 +1615,15 @@
           <t>AC-14 AC-15／F-05 F-10 F-13 F-23</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>権限を変更・解除する／権限をメンバーに割り当てる 方法1（すでに別の権限をお持ちの方）</t>
+        </is>
+      </c>
       <c r="J24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25" ht="88" customHeight="1">
+      <c r="K24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="94" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>割当</t>
@@ -1548,10 +1664,15 @@
           <t>AC-15／F-10</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>権限をメンバーに割り当てる 方法1（対象は自動で絞り込まれます）</t>
+        </is>
+      </c>
       <c r="J25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="88" customHeight="1">
+      <c r="K25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="94" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t>割当</t>
@@ -1592,10 +1713,15 @@
           <t>AC-17 AC-18／F-24</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>よくあるご質問（自分の権限を変更できますか）</t>
+        </is>
+      </c>
       <c r="J26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27" ht="88" customHeight="1">
+      <c r="K26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="94" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>割当</t>
@@ -1636,10 +1762,15 @@
           <t>AC-04 AC-19／F-14 F-15</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>権限を変更・解除する（権限を外す）／担当店舗を設定する（1つ以上お選びください）</t>
+        </is>
+      </c>
       <c r="J27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="88" customHeight="1">
+      <c r="K27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="94" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
           <t>指標</t>
@@ -1680,10 +1811,15 @@
           <t>AC-25／F-16</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>表示する数字を選ぶ（初期値は自動で設定されます）</t>
+        </is>
+      </c>
       <c r="J28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29" ht="88" customHeight="1">
+      <c r="K28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="94" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>指標</t>
@@ -1724,10 +1860,15 @@
           <t>AC-29 AC-30／F-17 F-18 F-19 F-20</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>表示する数字を選ぶ（指標条件設定 ＋ マイテンプレート）／オーナーだけができること</t>
+        </is>
+      </c>
       <c r="J29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="88" customHeight="1">
+      <c r="K29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="94" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>移植</t>
@@ -1768,10 +1909,15 @@
           <t>AC-01 AC-02 AC-03 AC-04</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>—（現行からの移植。顧客向けの記載なし）</t>
+        </is>
+      </c>
       <c r="J30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31" ht="88" customHeight="1">
+      <c r="K30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="94" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
           <t>設計レビュー</t>
@@ -1812,10 +1958,15 @@
           <t>K-01 K-02 K-03 K-04 K-05 K-06 AC-12／F-11 F-14 F-16 F-22</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>—（設計レビュー。顧客向けの記載なし）</t>
+        </is>
+      </c>
       <c r="J31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="88" customHeight="1">
+      <c r="K31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="94" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
           <t>判定</t>
@@ -1856,10 +2007,15 @@
           <t>AC-22 AC-32</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（6ケースすべて）</t>
+        </is>
+      </c>
       <c r="J32" s="3" t="inlineStr"/>
-    </row>
-    <row r="33" ht="88" customHeight="1">
+      <c r="K32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="94" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
           <t>次段階</t>
@@ -1900,15 +2056,20 @@
           <t>AC-23 AC-24 AC-25 AC-26</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>よくあるご質問（画面は見せたいが、変更はさせたくない場合）／担当店舗を設定する（今回のリリースでは、担当店舗は割り当ての記録として保存）</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J3:J33">
+  <conditionalFormatting sqref="K3:K33">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -1917,7 +2078,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J3:J33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K3:K33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,検証不能"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="列仕様" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +36,21 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E5F"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="005B6B7C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +60,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F7A8C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF3F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,15 +94,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,6 +488,569 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>検証プラン 列仕様</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>計算系と操作系を統合した1枚です。計算系だけに使う列（入力値・計算根拠）は、操作系では「—」になります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>列名</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>何を書くか</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>記入者</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>例</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>段階</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>準備／設定／権限が効くか／割当／一覧・遷移／指標／移植 のどれか。上から順に実施する</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>権限が効くか</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>検証ID</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>S＝準備、T＝検証。実施順に並べている</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>T-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>検証内容</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>何を確かめるケースか。ひと言で</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>US-03 エリア長（店長ベースのカスタマイズ例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>どの画面を開くか。ログインするユーザーも書く</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>US-03でログイン → 売上分析・従業員管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>前提・入力値</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>先に済んでいる必要のある準備ID。計算系はここに入力値を書く</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>S-05／入力値：担当店舗＝渋谷店・新宿店</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>実際に行う手順。クリックする場所まで書く</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>US-03でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>期待挙動</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>何が起きればよいか（できること）</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>担当2店舗の合計＝3,000,000 になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>起きてはいけないこと</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>何が出たらNGか（見えてはいけないもの）。権限の検証は「見えないこと」を確かめる場面が多いため独立させている</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>池袋（400万）が混ざらない。池袋三郎の給与80万が出ない</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>合否ライン</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>OK/NGを分ける数値の線。件数・割合・金額で書く</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>集計の合計＝3,000,000。池袋の混入＝0件（7,000,000ならNG）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>計算根拠</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>その数値になる理由。計算系のみ。操作系は「—」</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>渋谷100万＋新宿200万＝300万。池袋400万が入ると700万になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>確認ポイント</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>なぜこれを見るのか、どこで間違えやすいか</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>合計が7,000,000なら全社が見えている＝NG。P3を前倒しする根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>スクショファイル名</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>証跡の保存名。検証IDと合わせる</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>実施時</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>T-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>受入条件ID</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>この検証が担保する受入条件。NGならリリース判断に跳ね返る</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>AC-10 AC-11 AC-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>遷移フローID</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>対応する遷移フロー（20260803_09）。NGなら遷移の設計に跳ね返る</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>F-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>ヘルプページの該当箇所</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>顧客に何と説明しているか。NGならヘルプの記述も直す必要がある</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（複数の店舗をまとめて見せたい）／担当店舗を設定する（図2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>実際の値</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>実施して見えた値・挙動をそのまま書く。判断は書かない</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>実施時</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>合計 3,000,000。池袋は切替に出ず</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>OK／NG／検証不能。データを投入できない場合は「検証不能」。「問題なし」と書かない</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>実施時</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>■ 使い方</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>1. 「画面」を開き、「前提・入力値」が済んでいることを確かめる</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>2. 「操作」のとおりに操作する</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>3. 「期待挙動」と「起きてはいけないこと」の両方を見る</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>4. 「合否ライン」に照らして「実際の値」と「判定」を書く</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>5. NG のときは「受入条件ID」「遷移フローID」「ヘルプページの該当箇所」を見て、どこに跳ね返るかを確認する</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -488,7 +1074,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>確かめる手順。上から順に実施する。S-01〜S-06 は準備、T-01〜 が検証。
 「画面」を開いて「操作」を行い、「期待挙動」と「起きてはいけないこと」を見て、「合否ライン」に照らして「判定」に OK / NG を入れる。
@@ -497,2540 +1083,2540 @@
       </c>
     </row>
     <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>検証ID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>検証内容</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>前提・入力値</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>期待挙動</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>起きてはいけないこと</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>合否ライン</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>計算根拠</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>確認ポイント</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>スクショファイル名</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>受入条件ID</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>遷移フローID</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>ヘルプページの該当箇所</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>実際の値</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
     </row>
     <row r="3" ht="120" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>準備</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>環境とモックの確認</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>権限設定（ステージング）／仕様モック</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>ステージングURL（＝________）を開く。仕様モック https://suguru789987.github.io/rakmy-permission-mock/ も開き build版数が最新か確認。仕様書05 §8-6の確認事項をエンジニアに聞く</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>両方が開ける。エンジニアへの確認事項に回答がある</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>両方開ける＝2/2。確認事項の未回答＝0件</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>本番 rakmy／rakmy_server に触れていないこと</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>—（環境確認）</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="120" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>準備</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>S-02</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ投入</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>店舗管理／各実績の登録画面</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>S-01／入力値：渋谷100万／新宿200万／池袋400万、仕入は各1/10、人件費は売上の30%</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>20260803_10 の dataset/01〜06 を投入（店舗3件、売上1:2:4＝100万/200万/400万、仕入・人件費・従業員4名・費用・予算）</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>3店舗と当月1日分の実績が登録済み</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>3店舗×5種の実績が登録済み。比率 1：2：4 が崩れていない</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>1：2：4。合計からどの店舗が含まれるか一意に逆算できる</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>金額の比率 1：2：4 を崩さない</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>S-02</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>—（データ投入）</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>準備</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>S-03</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>検証ユーザー登録</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>ユーザー管理</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>S-02</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>dataset/07 の US-01〜07 を登録</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>検証ユーザー8名が登録済み</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>8名が登録済み</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>メールは +pm01〜08 で区別する</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>S-03</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>—（ユーザーの登録）</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="120" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>準備</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>S-04</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>権限6件の作成</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>権限設定 → ＋権限を新規作成</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>dataset/08 のとおり作成（経理担当（会社）・経理担当（店舗）・人事担当・エリア長・バイトリーダー・閲覧のみ・スタッフ の7権限）。**エリア長は既定テンプレートに無い＝店長を雛形に選び、権限名を『検証_エリア長』に変えて作る**（顧客が実際に行うカスタマイズの再現）。保存後に再度開いて設定が再現するか確認</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>7権限が保存でき、再表示で設定が再現する</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>欠落・反転が起きない</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>7権限が保存でき、再表示で欠落・反転＝0件</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>保存が壊れると以降の検証がすべて無意味になる</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>S-04</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>AC-07</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>F-03</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>ケース別のやり方</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="120" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>準備</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>割当と担当店舗</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>権限設定 → ユーザー割当 → 割当を編集</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>S-03 S-04</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>dataset/07 のとおり割当（US-01=経理（会社）／US-08=経理（店舗）全店／US-03=渋谷・新宿／US-04・US-06=渋谷／US-07は付け替え用）</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>全員に割当が保存され、店舗の権限に担当店舗が付く</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>会社の権限に担当店舗欄が出ない</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>8名すべてに割当が保存。店舗の権限の担当店舗が未設定＝0件</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>US-08 は担当店舗＝全店</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>AC-14 AC-16</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>F-11 F-14</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>権限をメンバーに割り当てる／担当店舗を設定する</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>準備</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>S-06</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>移植前スクショ取得</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>各画面（プリセット適用前）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>プリセット適用前に master／manager／shop_manager でログインし全メニューをスクショ</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>master／manager／shop_manager の3権限分のスクショを取得</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>3権限分のスクショを取得＝3/3</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>リリース前にしか取れない。最優先</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>S-06×3</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>AC-01</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>—（移植前の記録）</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>設定</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>T-01</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>基本情報・雛形・デモモード</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>権限編集 → 基本情報</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>新規作成を開き入力項目を記録。雛形（ベース）の候補を確認。ヘッダーで新規導入デモ／運用デモを切り替える</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>雛形の候補に移植プリセットと「まっさら（なし）」が出る。運用デモでは「既存権限をコピー」が増える</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>雛形の候補＝4種＋まっさら（なし）。エリア長は含まれない</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>項目名を記録（仕様=権限名/区分、実装=キー/ロール名/種別）。UI変更依頼の根拠になる</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>T-01</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>AC-08</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>F-03 F-26</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>権限を作成する STEP 2　雛形を選ぶ／STEP 3　権限名と区分を決める</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>設定</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>T-02</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>初期値と既定の安全側</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>権限編集 → 基本情報／権限内容</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>雛形＝「まっさら（なし）」を選び許可数を確認。既存と同じキーで保存、キー空欄でも保存。新規画面追加時の既定値をエンジニアに確認</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>「まっさら（なし）」を選ぶと許可0件</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>キー重複はエラーになる。新規画面の既定は「なし」</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>まっさらの許可＝0件。キー重複＝エラー。新規画面の既定＝なし（例外0件）</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>既定が許可側だと画面が増えるたび全員に見えてしまう</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>T-02</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>AC-09 AC-12</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>権限を作成する STEP 2（まっさら（なし））／よくあるご質問（新しい画面が追加された場合）</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr"/>
+      <c r="Q10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="120" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>設定</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>T-03</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>区分の出し分けと画面数</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>権限編集 → 権限内容（区分を切替）</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>S-01／入力値：区分＝会社／店舗を切替</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>新規作成で区分を会社→店舗に切替。それぞれ全展開してカテゴリ数を数える</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>区分=会社で21カテゴリ、区分=店舗で23カテゴリ</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>会社で店舗専用6が出ない／店舗で会社専用4が出ない</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>会社＝21カテゴリ／店舗＝23カテゴリ。総数27カテゴリ53機能</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>共通17 ＋ 会社4 ＝ 21／共通17 ＋ 店舗6 ＝ 23。総数27カテゴリ53機能</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>総数27カテゴリ53機能。数え間違いに注意</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>T-03</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>AC-05 AC-06</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>F-21</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>権限を作成する STEP 3（図3 会社と店舗の区分）</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="120" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>設定</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>権限テンプレートの保存と破棄</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>権限テンプレート（初回表示）</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>権限テンプレート画面で選択途中に「一時保存」→離れて再訪→次に「下書きを破棄」→「適用」</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>一時保存した選択が再訪で復元。適用で権限一覧に登録</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>破棄すると既定に戻る</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>一時保存の復元＝一致。破棄で既定に戻る。適用で権限一覧に4権限が登録</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>導入時に顧客が最初に触れる画面</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>AC-33</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>F-01 F-02 F-25</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>導入時の初期設定</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="P12" s="4" t="inlineStr"/>
+      <c r="Q12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="120" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>一覧・遷移</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>T-05</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>一覧の許可数と表示の保持</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>権限一覧</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>S-04／入力値：7権限それぞれの設定値</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>**7権限すべての**一覧タブ／設定タブの内訳を数える。表示ロール・権限列設定を変更→離れて再訪</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>7権限すべてで一覧の許可数＝実際の設定。列選択が次回も保持（スコープ別）</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>不一致が0件</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>7権限すべてで許可数の不一致＝0件。列選択が次回も一致（スコープ別）</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>許可数＝dataset/08 の「なし」以外の行数。閲覧タブ7項目・設定タブ14項目で数える</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>数値例＝経理(会社)閲覧4/7・設定3／人事 閲覧2/7／バイトL 閲覧1/7／閲覧のみ 閲覧7/7・設定14</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>T-05</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>AC-20 AC-31</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>F-22</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>設定内容を確認する（権限一覧）</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="P13" s="4" t="inlineStr"/>
+      <c r="Q13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="120" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>一覧・遷移</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>T-06</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>役割サマリの人数と絞り込み</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>役割サマリ → 割当へ →</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>S-05／入力値：7権限それぞれの割当人数</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>役割サマリの「割当ユーザー N名」と実保持者数を突合。「割当へ →」を選択</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>7権限すべてで表示人数＝実保持者数。保持者だけに絞り込まれる</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>差分が0件</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>7権限すべてで 表示人数＝実保持者数（差分0）</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>表示人数＝dataset/07 でその権限を割り当てたユーザーの件数</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>保持者0名なら絞り込まず全件＋案内バナー</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>T-06</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>AC-28</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>F-12</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>設定内容を確認する（役割サマリ）／権限をメンバーに割り当てる 方法3</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="P14" s="4" t="inlineStr"/>
+      <c r="Q14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="120" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>一覧・遷移</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>T-07</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>権限編集の4入口と戻り先</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>権限一覧／一覧のマス目／役割サマリ／割当編集</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>一覧の行／一覧のマス目／役割サマリ／割当編集 の4か所から権限編集に入り、保存して着地を確認。あわせて割当編集の「＋権限を新規作成」も</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>4入口とも保存後に来た元へ戻る。マス目からは該当箇所へ移動＋ハイライト</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>4入口すべてで来た元に戻る＝4/4。マス目からの移動＋ハイライトあり</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>割当編集からの新規作成はベースが「まっさら（なし）」既定</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>T-07</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>AC-27</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>F-04 F-06 F-07 F-08 F-09</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>作成した権限を修正する（入口の一覧表）</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="P15" s="4" t="inlineStr"/>
+      <c r="Q15" s="4" t="inlineStr"/>
     </row>
     <row r="16" ht="120" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>一覧・遷移</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>T-08</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>変更の反映タイミング</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>対象ユーザーでログインした画面</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>検証_エリア長（店長ベースで作成）から売上分析をオフにして保存→US-03のセッションで画面遷移→確認後に元へ戻す</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>設定変更後、次の画面遷移または再ログインで反映される</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>無反映が0件</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>無反映＝0件。即時か再ログインかを記録</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>即時か再ログインかを必ず記録する（ヘルプの記載と揃える）</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>AC-21</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>F-06</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>よくあるご質問（設定した権限はいつから反映されますか）</t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="P16" s="4" t="inlineStr"/>
+      <c r="Q16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="120" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>権限が効くか</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>T-09</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>US-01 経理（会社）</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>US-01でログイン → 各画面</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>US-01（経理・区分=会社）でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>売上分析・仕入分析・詳細分析・集計・お支払いの5画面が開ける</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>従業員管理・従業員（閲覧）・権限設定がメニューに出ず、直URLでも開けない</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>開ける5画面＝100%。開けない3画面＝100%（メニュー非表示かつ直URLも塞ぐ）</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>費用設定・予算設定は店舗画面のため会社スコープに存在しない</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>T-09</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>AC-10 AC-11</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>F-11</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>ケース別のやり方（経理担当に、売上とお支払だけ見せたい）</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="P17" s="4" t="inlineStr"/>
+      <c r="Q17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="120" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>権限が効くか</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>T-09b</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>US-08 経理（店舗・全店）</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>US-08でログイン → 各画面</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>US-08（経理・区分=店舗／担当店舗=全店）でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>売上分析・仕入分析・詳細分析・集計・費用設定・予算設定の6画面が開け、3店舗すべてのデータが見える</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>従業員管理・従業員（閲覧）・権限設定が開けない</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>開ける6画面＝100%かつ3店舗すべてのデータが見える。開けない3画面＝100%</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>お支払いは会社画面のため店舗スコープに存在しない</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>T-09b</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>AC-10 AC-11 AC-16</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>F-11</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>ケース別のやり方（経理担当に、売上とお支払だけ見せたい ＋ 会社と店舗の両方の画面を使わせたい）</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="P18" s="4" t="inlineStr"/>
+      <c r="Q18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="120" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>権限が効くか</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>T-10</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>US-02 人事</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>US-02でログイン → ダッシュボード・従業員管理</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>US-02 人事でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>従業員情報と締め管理が見える</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>売上分析・仕入分析・詳細分析・集計・お支払いが開けない。ダッシュボードに売上が出ない</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>開ける画面＝従業員関連のみ。売上系5画面＝0件。ダッシュボードに売上が出ない</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>データが空だと「塞げている」のか区別できない。S-02 の投入が前提</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>T-10</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>AC-10 AC-11</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>F-11</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>ケース別のやり方（人事担当に、従業員情報だけ見せたい）</t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="P19" s="4" t="inlineStr"/>
+      <c r="Q19" s="4" t="inlineStr"/>
     </row>
     <row r="20" ht="120" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>権限が効くか</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>T-11</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>US-03 エリア長（店長ベースのカスタマイズ例）</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>US-03でログイン → 売上分析・従業員管理</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>S-05／入力値：担当店舗＝渋谷店・新宿店</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>US-03 検証_エリア長でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>担当2店舗の合計＝3,000,000 になる</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>池袋（400万）が混ざらない。池袋三郎の給与80万が出ない</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>集計の合計＝3,000,000。池袋の混入＝0件（7,000,000ならNG）。給与80万の表示＝0件</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>渋谷100万＋新宿200万＝300万。池袋400万が入ると700万になるため、合計を見れば混入を特定できる</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>合計が7,000,000なら全社が見えている＝NG。P3を前倒しする根拠</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>T-11</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>AC-10 AC-11 AC-23</t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>F-14</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>ケース別のやり方（複数の店舗をまとめて見せたい）／担当店舗を設定する（図2）</t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="P20" s="4" t="inlineStr"/>
+      <c r="Q20" s="4" t="inlineStr"/>
     </row>
     <row r="21" ht="120" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>権限が効くか</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>T-12</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>US-04 バイトL</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>US-04でログイン → 売上分析</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>S-05／入力値：原価率は全店10%</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>US-04 バイトLでログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>売上と日々の入力画面が開ける</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>仕入分析・詳細分析・従業員管理・締め管理・費用設定・予算設定が開けない。原価率が出ない</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>開ける16画面＝100%。開けない7画面＝0件。原価率の表示＝0件</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>率を揃えているため、値の妥当性ではなく「原価率」という項目の有無だけを見る</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>原価率は全店10%に揃えてある。項目の有無だけを見る</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>T-12</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>AC-10 AC-11</t>
         </is>
       </c>
-      <c r="N21" s="3" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>F-11</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>ケース別のやり方（アルバイトリーダーに、一部の画面だけ見せたい）</t>
         </is>
       </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="P21" s="4" t="inlineStr"/>
+      <c r="Q21" s="4" t="inlineStr"/>
     </row>
     <row r="22" ht="120" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>権限が効くか</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>T-13</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>US-05 閲覧のみ</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>US-05でログイン → 会社スコープの各画面</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>US-05 閲覧のみでログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>会社スコープの全21画面が開ける</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>—（更新できてしまうかは T-23 で記録）</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>会社スコープの21画面が開ける＝100%</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>費用設定など店舗専用画面は会社スコープに存在しない</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>T-13</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>AC-10 AC-11</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>F-11</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>権限を作成する STEP 4（「閲覧」と「操作」は、今回のリリースではどちらも）</t>
         </is>
       </c>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="P22" s="4" t="inlineStr"/>
+      <c r="Q22" s="4" t="inlineStr"/>
     </row>
     <row r="23" ht="120" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>権限が効くか</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>T-14</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>US-06 スタッフ</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>US-06でログイン → ログイン直後</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>US-06 スタッフでログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>ログインでき、ダッシュボードに着地する</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>ダッシュボード以外が開けない</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>ログインでき、開ける画面＝1（ダッシュボードのみ）。空白・エラー・ループ＝0件</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>空白・エラー・ループが0件。最小権限でも締め出さない</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>T-14</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>AC-10 AC-11 AC-13</t>
         </is>
       </c>
-      <c r="N23" s="3" t="inlineStr">
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>F-11</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>ケース別のやり方（新しく入った方には、まず最小限から始めたい）／よくあるご質問（権限を絞りすぎて、何も見えなくなりませんか）</t>
         </is>
       </c>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="P23" s="4" t="inlineStr"/>
+      <c r="Q23" s="4" t="inlineStr"/>
     </row>
     <row r="24" ht="120" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>割当</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>T-15</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>権限の付け替えと置き換えの明示</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>ユーザー割当 → 割当を編集</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>US-07（検証_エリア長・店舗）の割当編集で 検証_経理担当（会社）に付け替え、行の表示を確認してから保存→US-07でログイン</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>別の権限を選んで保存すると前の権限が外れる。行に「選ぶと『◯◯』から置き換わります」が出る</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>権限を2つ同時に選べない</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>同時に選べる権限＝1つ。付け替え後に前の権限の画面＝0件。置換予告の表示＝100%</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>エリア長→経理（会社）に付け替えると担当店舗欄が消える</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>T-15</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>AC-14 AC-15</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>F-05 F-10 F-13 F-23</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>権限を変更・解除する／権限をメンバーに割り当てる 方法1（すでに別の権限をお持ちの方）</t>
         </is>
       </c>
-      <c r="P24" s="3" t="inlineStr"/>
-      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="P24" s="4" t="inlineStr"/>
+      <c r="Q24" s="4" t="inlineStr"/>
     </row>
     <row r="25" ht="120" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>割当</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>T-16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>区分フィルタ</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>一括割当（権限起点）</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>検証_エリア長（店舗）で一括割当を開く→「すべて表示」</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>店舗の権限では店舗所属、会社の権限では本部所属が表示される。「すべて表示」で解除できる</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>区分に応じた絞り込みが効く。「すべて表示」で全員が出る</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>店舗ロール＆含める＆店舗0件はエラー</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>T-16</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>AC-15</t>
         </is>
       </c>
-      <c r="N25" s="3" t="inlineStr">
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>F-10</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>権限をメンバーに割り当てる 方法1（対象は自動で絞り込まれます）</t>
         </is>
       </c>
-      <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="P25" s="4" t="inlineStr"/>
+      <c r="Q25" s="4" t="inlineStr"/>
     </row>
     <row r="26" ht="120" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>割当</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>T-17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>締め出しと越権の防止</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>権限編集（自ロール）／権限設定のURL直打ち</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>S-01 S-05</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>自ロールから権限設定をなしにして保存を試みる。次にUS-04（店舗）で権限設定のURLを直接開く</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>自ロールから権限設定を外すと警告が出る、または最後の全権は外せない</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>一般の権限で権限設定が開けない</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>無警告で保存できる＝0件。一般の権限で権限設定が開ける＝0件</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>無警告で保存できてしまうと自分を締め出せる</t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>T-17</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>AC-17 AC-18</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr">
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>F-24</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>よくあるご質問（自分の権限を変更できますか）</t>
         </is>
       </c>
-      <c r="P26" s="3" t="inlineStr"/>
-      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="P26" s="4" t="inlineStr"/>
+      <c r="Q26" s="4" t="inlineStr"/>
     </row>
     <row r="27" ht="120" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>割当</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>T-18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>権限を外す・店舗未紐付け</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>ユーザー割当 → 割当を編集</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>US-06の割当編集で「割当なし」を選び保存→ログイン確認→S-05に戻す。次に店舗を選ばず店舗の権限を割当して保存</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>「割当なし」で保存すると未割当になり、ログインしても画面が出ない</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>担当店舗0件では保存できない、または警告が出る</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>未割当で開ける画面＝0件。担当店舗0件のまま保存できる＝0件</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>権限設定画面に「⚠ ◯名が店舗未設定」が出る</t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>T-18</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>AC-04 AC-19</t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr">
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>F-14 F-15</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>権限を変更・解除する（権限を外す）／担当店舗を設定する（1つ以上お選びください）</t>
         </is>
       </c>
-      <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="P27" s="4" t="inlineStr"/>
+      <c r="Q27" s="4" t="inlineStr"/>
     </row>
     <row r="28" ht="120" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>T-19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>指標一覧と既定件数</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>権限一覧 → 指標一覧</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>S-05／入力値：7権限それぞれの雛形</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>スタッフ・検証_エリア長・経理の指標一覧を開き、店舗／会社タブのON件数を数える。任意の指標をON/OFF</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>従業員ベース=店舗17/会社0、店長ベース=店舗36/会社8、本部管理ベース=店舗36/会社25</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>保存ボタンが無く、切替はその場で反映される</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>7権限すべてで dataset/09 の値と一致（差分0）。保存ボタン＝なし</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>指標の既定は雛形で決まる。従業員＝openのみON（店舗17/会社0）、店長＝open＋mgr（36/8）、本部管理＝全件（36/25）</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>7権限すべてを dataset/09 の値と突合する</t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>T-19</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>AC-25</t>
         </is>
       </c>
-      <c r="N28" s="3" t="inlineStr">
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>F-16</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>表示する数字を選ぶ（初期値は自動で設定されます）</t>
         </is>
       </c>
-      <c r="P28" s="3" t="inlineStr"/>
-      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="P28" s="4" t="inlineStr"/>
+      <c r="Q28" s="4" t="inlineStr"/>
     </row>
     <row r="29" ht="120" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>T-20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>一括設定・再利用・オーナー専用</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>指標条件設定／マイテンプレート／👑オーナー操作</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>指標条件設定で推奨テンプレ「店長向け」を適用（キャンセルとの差も確認）→マイテンプレートに保存→別の権限で読込。次に「👑オーナー操作」の指標管理と付与先指定</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>おすすめの組み合わせを適用でき、名前をつけて保存して他権限で読込できる</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>指標管理に編集UI（トグル/コピー/条件設定）が出ない。オーナー以外が付与先指定を実行できない</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>テンプレ適用の結果が定義と一致。指標管理に編集UI＝0件。オーナー以外の付与先指定＝0件</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>「適用して指標一覧へ」まで反映されない。キャンセルは非適用</t>
         </is>
       </c>
-      <c r="L29" s="3" t="inlineStr">
+      <c r="L29" s="4" t="inlineStr">
         <is>
           <t>T-20</t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>AC-29 AC-30</t>
         </is>
       </c>
-      <c r="N29" s="3" t="inlineStr">
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>F-17 F-18 F-19 F-20</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>表示する数字を選ぶ（指標条件設定 ＋ マイテンプレート）／オーナーだけができること</t>
         </is>
       </c>
-      <c r="P29" s="3" t="inlineStr"/>
-      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="P29" s="4" t="inlineStr"/>
+      <c r="Q29" s="4" t="inlineStr"/>
     </row>
     <row r="30" ht="120" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>移植</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>T-21</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>現行3権限の移植と漏れ</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>権限一覧（プリセット適用後）</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>S-06</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>プリセット適用後に master／manager／shop_manager で全メニューを再取得しS-06と突合。ユーザー割当一覧で未割当を数える</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>master／manager／shop_manager と同じ動作のプリセットがある</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>適用前後で見える画面の増減が0</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>3権限とも適用前後で見える画面の増減＝0</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>S-06 のスクショと1画面ずつ突き合わせる</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
         <is>
           <t>T-21×3</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>AC-01 AC-02 AC-03 AC-04</t>
         </is>
       </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>—（現行からの移植。顧客向けの記載なし）</t>
         </is>
       </c>
-      <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="P30" s="4" t="inlineStr"/>
+      <c r="Q30" s="4" t="inlineStr"/>
     </row>
     <row r="31" ht="120" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>設計レビュー</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>境界設計の確認（動作テストでは検出できない）</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>エンジニアと画面・APIを一緒に棚卸し</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>エンジニアと画面・APIを一緒に棚卸しし、7点を確認する。①ユーザー個別に権限内容を編集できるUI/APIが無いか ②店舗ロールでも担当店舗を全店・複数店に設定できるか ③権限の状態が なし/閲覧/操作 の3つだけか ④指標一覧に機密度のバッジが出ていないか ⑤店舗ロールの指標一覧で会社指標をONにできるか（既定OFF）⑥一括割当で店舗を選んだだけでは権限が付与されないか ⑦画面カテゴリを新しく追加したとき、既存の全権限で既定が「なし」になるか（AC-12 のコード上の既定値を確認）</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>7点すべてが設計どおり</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>7点すべてが設計どおり（1つでも崩れていればNG）</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>動くかどうかではなく「そう作られているか」を見る</t>
         </is>
       </c>
-      <c r="L31" s="3" t="inlineStr">
+      <c r="L31" s="4" t="inlineStr">
         <is>
           <t>T-24_レビュー記録</t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>K-01 K-02 K-03 K-04 K-05 K-06 AC-12</t>
         </is>
       </c>
-      <c r="N31" s="3" t="inlineStr">
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>F-11 F-14 F-16 F-22</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>—（設計レビュー。顧客向けの記載なし）</t>
         </is>
       </c>
-      <c r="P31" s="3" t="inlineStr"/>
-      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="P31" s="4" t="inlineStr"/>
+      <c r="Q31" s="4" t="inlineStr"/>
     </row>
     <row r="32" ht="120" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>T-22</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>7シナリオの意図判定</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>これまでの結果をまとめて判定</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>T-09〜T-14 T-20</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>各シナリオが意図どおり作れたかを判定</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>SC-01a/01b/02/04/06 の5件で ×（作れない）が0件</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>SC-01a/01b/02/04/06 の5件で ×＝0件</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>SC-03・SC-05 は P1 では×が想定。判定せず記録する</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="M32" s="4" t="inlineStr">
         <is>
           <t>AC-22 AC-32</t>
         </is>
       </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>ケース別のやり方（6ケースすべて）</t>
         </is>
       </c>
-      <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="P32" s="4" t="inlineStr"/>
+      <c r="Q32" s="4" t="inlineStr"/>
     </row>
     <row r="33" ht="120" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>次段階</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>T-23</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>対象外4項目の実測</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>US-05で会社情報／US-03の合計／US-02の指標／操作ログ</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>S-05 T-11／入力値：US-05／US-03／US-02／操作ログ</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>①US-05（閲覧のみ・区分=会社）で会社情報を変更し保存（値が更新されるか）②T-11の合計が3,000,000だったか ③US-02のダッシュボード等に出る指標を数える ④権限の作成・割当の操作ログを確認</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>判定せず実測のみ記録</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>判定せず実測を記録（①更新可否 ②合計値 ③指標数 ④ログ有無）</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>②の合計が7,000,000なら全社が見えている＝P3が必要という判断根拠になる</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>①更新できる→P2が必要 ②700万→P3が必要 ③許可外の指標が出る→P4が必要 ④ログが無い→P5が必要</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="L33" s="4" t="inlineStr">
         <is>
           <t>T-23</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>AC-23 AC-24 AC-25 AC-26</t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>よくあるご質問（画面は見せたいが、変更はさせたくない場合）／担当店舗を設定する（今回のリリースでは、担当店舗は割り当ての記録として保存）</t>
         </is>
       </c>
-      <c r="P33" s="3" t="inlineStr"/>
-      <c r="Q33" s="3" t="inlineStr">
+      <c r="P33" s="4" t="inlineStr"/>
+      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>

--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -1345,7 +1345,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>ユーザー管理</t>
+          <t>ユーザー管理（経営管理クラウドの管理者登録画面）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>雛形の候補に「エリア長」が出ない（既定テンプレートではないため）</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>権限一覧</t>
+          <t>権限一覧（閲覧タブ／設定タブを切り替え、👤表示ロール・📌権限列設定も操作する）</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>入口と違う画面に着地しない。マス目から入ったときに該当箇所が開かず先頭に戻る、ということが起きない</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>US-01でログイン → 各画面</t>
+          <t>US-01でログイン → 売上分析／仕入分析／詳細分析／集計／お支払い（開ける）＋ 従業員管理／従業員（閲覧）／権限設定（開けない）</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>US-08でログイン → 各画面</t>
+          <t>US-08でログイン → 売上分析／仕入分析／詳細分析／集計／費用設定／予算設定（開ける）＋ 従業員管理／従業員（閲覧）／権限設定（開けない）</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>US-05でログイン → 会社スコープの各画面</t>
+          <t>US-05でログイン → 会社スコープの全21画面（ダッシュボード・売上分析・仕入分析・詳細分析・集計・従業員関連・会社情報・お支払い・店舗（管理）・ダウンロード ほか）</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>一括割当（権限起点）</t>
+          <t>一括割当（ヘルプの「方法1 まとめて割り当てる」）</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>店舗の権限で「含める」にチェックしただけで担当店舗0件のまま保存できない</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>区分に応じた絞り込みが効く。「すべて表示」で全員が出る</t>
+          <t>店舗の権限で表示＝店舗所属のみ、会社の権限で表示＝本部所属のみ。「すべて表示」で8名全員が出る。店舗0件での保存＝0件</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7点のいずれかが設計と違う状態で「画面は動くから問題なし」と判定されない</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>×（作れない）が必須5シナリオに1件でも出ない</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>「問題なし」と書かない。実測値をそのまま記録する</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">

--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -1409,47 +1409,47 @@
     <row r="6" ht="120" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>準備</t>
+          <t>設定（S-04より前）</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>S-04</t>
+          <t>T-04</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>権限6件の作成</t>
+          <t>権限テンプレートの保存と破棄</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>権限設定 → ＋権限を新規作成</t>
+          <t>権限テンプレート（初回表示）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>S-01</t>
+          <t>S-01／権限を1件も作っていない初回状態</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>dataset/08 のとおり作成（経理担当（会社）・経理担当（店舗）・人事担当・エリア長・バイトリーダー・閲覧のみ・スタッフ の7権限）。**エリア長は既定テンプレートに無い＝店長を雛形に選び、権限名を『検証_エリア長』に変えて作る**（顧客が実際に行うカスタマイズの再現）。保存後に再度開いて設定が再現するか確認</t>
+          <t>権限テンプレート画面で選択途中に「一時保存」→離れて再訪→次に「下書きを破棄」→「適用」</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>7権限が保存でき、再表示で設定が再現する</t>
+          <t>一時保存した選択が再訪で復元。適用で権限一覧に登録</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>欠落・反転が起きない</t>
+          <t>権限を作成済みの状態で実施して「画面が出ない＝NG」と誤判定しない</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>7権限が保存でき、再表示で欠落・反転＝0件</t>
+          <t>一時保存の復元＝一致。破棄で既定に戻る。適用で権限一覧に4権限が登録</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -1459,27 +1459,27 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>保存が壊れると以降の検証がすべて無意味になる</t>
+          <t>導入時に顧客が最初に触れる画面。権限を作った後だとこの画面が出ないため、必ず S-04 より前に実施する</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>S-04</t>
+          <t>T-04</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>AC-07</t>
+          <t>AC-33</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-01 F-02 F-25</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>ケース別のやり方</t>
+          <t>導入時の初期設定</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr"/>
@@ -1493,42 +1493,42 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>割当と担当店舗</t>
+          <t>権限7件の作成</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>権限設定 → ユーザー割当 → 割当を編集</t>
+          <t>権限設定 → ＋権限を新規作成</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>S-03 S-04</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>dataset/07 のとおり割当（US-01=経理（会社）／US-08=経理（店舗）全店／US-03=渋谷・新宿／US-04・US-06=渋谷／US-07は付け替え用）</t>
+          <t>dataset/08 のとおり作成（経理担当（会社）・経理担当（店舗）・人事担当・エリア長・バイトリーダー・閲覧のみ・スタッフ の7権限）。**エリア長は既定テンプレートに無い＝店長を雛形に選び、権限名を『検証_エリア長』に変えて作る**（顧客が実際に行うカスタマイズの再現）。保存後に再度開いて設定が再現するか確認</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>全員に割当が保存され、店舗の権限に担当店舗が付く</t>
+          <t>7権限が保存でき、再表示で設定が再現する</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>会社の権限に担当店舗欄が出ない</t>
+          <t>欠落・反転が起きない</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8名すべてに割当が保存。店舗の権限の担当店舗が未設定＝0件</t>
+          <t>7権限が保存でき、再表示で欠落・反転＝0件</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1538,27 +1538,27 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>US-08 は担当店舗＝全店</t>
+          <t>保存が壊れると以降の検証がすべて無意味になる</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>AC-14 AC-16</t>
+          <t>AC-07</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>F-11 F-14</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>権限をメンバーに割り当てる／担当店舗を設定する</t>
+          <t>ケース別のやり方</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr"/>
@@ -1572,42 +1572,42 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>S-06</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>移植前スクショ取得</t>
+          <t>割当と担当店舗</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>各画面（プリセット適用前）</t>
+          <t>権限設定 → ユーザー割当 → 割当を編集</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>S-01</t>
+          <t>S-03 S-04</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>プリセット適用前に master／manager／shop_manager でログインし全メニューをスクショ</t>
+          <t>dataset/07 のとおり割当（US-01=経理（会社）／US-08=経理（店舗）全店／US-03=渋谷・新宿／US-04・US-06=渋谷／US-07は付け替え用）</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>master／manager／shop_manager の3権限分のスクショを取得</t>
+          <t>全員に割当が保存され、店舗の権限に担当店舗が付く</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>会社の権限に担当店舗欄が出ない</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>3権限分のスクショを取得＝3/3</t>
+          <t>8名すべてに割当が保存。店舗の権限の担当店舗が未設定＝0件</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1617,27 +1617,27 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>リリース前にしか取れない。最優先</t>
+          <t>US-08 は担当店舗＝全店</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>S-06×3</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>AC-01</t>
+          <t>AC-14 AC-16</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-11 F-14</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>—（移植前の記録）</t>
+          <t>権限をメンバーに割り当てる／担当店舗を設定する</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr"/>
@@ -1646,22 +1646,22 @@
     <row r="9" ht="120" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>設定</t>
+          <t>準備</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>S-06</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>基本情報・雛形・デモモード</t>
+          <t>移植前スクショ取得</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>権限編集 → 基本情報</t>
+          <t>各画面（プリセット適用前）</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1671,22 +1671,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>新規作成を開き入力項目を記録。雛形（ベース）の候補を確認。ヘッダーで新規導入デモ／運用デモを切り替える</t>
+          <t>プリセット適用前に master／manager／shop_manager でログインし全メニューをスクショ</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>雛形の候補に移植プリセットと「まっさら（なし）」が出る。運用デモでは「既存権限をコピー」が増える</t>
+          <t>master／manager／shop_manager の3権限分のスクショを取得</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>雛形の候補に「エリア長」が出ない（既定テンプレートではないため）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>雛形の候補＝4種＋まっさら（なし）。エリア長は含まれない</t>
+          <t>3権限分のスクショを取得＝3/3</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1696,27 +1696,27 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>項目名を記録（仕様=権限名/区分、実装=キー/ロール名/種別）。UI変更依頼の根拠になる</t>
+          <t>リリース前にしか取れない。最優先</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>S-06×3</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>AC-08</t>
+          <t>AC-01</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>F-03 F-26</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>権限を作成する STEP 2　雛形を選ぶ／STEP 3　権限名と区分を決める</t>
+          <t>—（移植前の記録）</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr"/>
@@ -1730,17 +1730,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>T-01</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>初期値と既定の安全側</t>
+          <t>基本情報・雛形・デモモード</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>権限編集 → 基本情報／権限内容</t>
+          <t>権限編集 → 基本情報</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1750,22 +1750,22 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>雛形＝「まっさら（なし）」を選び許可数を確認。既存と同じキーで保存、キー空欄でも保存。新規画面追加時の既定値をエンジニアに確認</t>
+          <t>新規作成を開き入力項目を記録。雛形（ベース）の候補を確認。ヘッダーで新規導入デモ／運用デモを切り替える</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>「まっさら（なし）」を選ぶと許可0件</t>
+          <t>雛形の候補に移植プリセットと「まっさら（なし）」が出る。運用デモでは「既存権限をコピー」が増える</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>キー重複はエラーになる。新規画面の既定は「なし」</t>
+          <t>雛形の候補に「エリア長」が出ない（既定テンプレートではないため）</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>まっさらの許可＝0件。キー重複＝エラー。新規画面の既定＝なし（例外0件）</t>
+          <t>雛形の候補＝4種＋まっさら（なし）。エリア長は含まれない</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1775,27 +1775,27 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>既定が許可側だと画面が増えるたび全員に見えてしまう</t>
+          <t>項目名を記録（仕様=権限名/区分、実装=キー/ロール名/種別）。UI変更依頼の根拠になる</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>T-01</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>AC-09 AC-12</t>
+          <t>AC-08</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-03 F-26</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>権限を作成する STEP 2（まっさら（なし））／よくあるご質問（新しい画面が追加された場合）</t>
+          <t>権限を作成する STEP 2　雛形を選ぶ／STEP 3　権限名と区分を決める</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr"/>
@@ -1809,72 +1809,72 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>T-03</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>区分の出し分けと画面数</t>
+          <t>初期値と既定の安全側</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>権限編集 → 権限内容（区分を切替）</t>
+          <t>権限編集 → 基本情報／権限内容</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>S-01／入力値：区分＝会社／店舗を切替</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>新規作成で区分を会社→店舗に切替。それぞれ全展開してカテゴリ数を数える</t>
+          <t>雛形＝「まっさら（なし）」を選び許可数を確認。既存と同じキーで保存、キー空欄でも保存。新規画面追加時の既定値をエンジニアに確認。**確認後、この検証で作った権限は必ず削除する**</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>区分=会社で21カテゴリ、区分=店舗で23カテゴリ</t>
+          <t>「まっさら（なし）」を選ぶと許可0件</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>会社で店舗専用6が出ない／店舗で会社専用4が出ない</t>
+          <t>キーの重複が保存できてしまう。**検証で作った権限を残したまま次に進まない（T-05／T-06 の件数が合わなくなる）**</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>会社＝21カテゴリ／店舗＝23カテゴリ。総数27カテゴリ53機能</t>
+          <t>まっさらの許可＝0件。キー重複＝エラー。新規画面の既定＝なし（例外0件）</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>共通17 ＋ 会社4 ＝ 21／共通17 ＋ 店舗6 ＝ 23。総数27カテゴリ53機能</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>総数27カテゴリ53機能。数え間違いに注意</t>
+          <t>既定が許可側だと画面が増えるたび全員に見えてしまう</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>T-03</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>AC-05 AC-06</t>
+          <t>AC-09 AC-12</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>F-21</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>権限を作成する STEP 3（図3 会社と店舗の区分）</t>
+          <t>権限を作成する STEP 2（まっさら（なし））／よくあるご質問（新しい画面が追加された場合）</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr"/>
@@ -1888,72 +1888,72 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>T-04</t>
+          <t>T-03</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>権限テンプレートの保存と破棄</t>
+          <t>区分の出し分けと画面数</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>権限テンプレート（初回表示）</t>
+          <t>権限編集 → 権限内容（区分を切替）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>S-01</t>
+          <t>S-01／入力値：区分＝会社／店舗を切替</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>権限テンプレート画面で選択途中に「一時保存」→離れて再訪→次に「下書きを破棄」→「適用」</t>
+          <t>新規作成で区分を会社→店舗に切替。それぞれ全展開してカテゴリ数を数える</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>一時保存した選択が再訪で復元。適用で権限一覧に登録</t>
+          <t>区分=会社で21カテゴリ、区分=店舗で23カテゴリ</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>破棄すると既定に戻る</t>
+          <t>会社で店舗専用6が出ない／店舗で会社専用4が出ない</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>一時保存の復元＝一致。破棄で既定に戻る。適用で権限一覧に4権限が登録</t>
+          <t>会社＝21カテゴリ／店舗＝23カテゴリ。総数27カテゴリ53機能</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>共通17 ＋ 会社4 ＝ 21／共通17 ＋ 店舗6 ＝ 23。総数27カテゴリ53機能</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>導入時に顧客が最初に触れる画面</t>
+          <t>総数27カテゴリ53機能。数え間違いに注意</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>T-04</t>
+          <t>T-03</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>AC-33</t>
+          <t>AC-05 AC-06</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>F-01 F-02 F-25</t>
+          <t>F-21</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>導入時の初期設定</t>
+          <t>権限を作成する STEP 3（図3 会社と店舗の区分）</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr"/>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>US-07（検証_エリア長・店舗）の割当編集で 検証_経理担当（会社）に付け替え、行の表示を確認してから保存→US-07でログイン</t>
+          <t>US-07（検証_エリア長・店舗）の割当編集で 検証_経理担当（会社）に付け替え、行の表示を確認してから保存→US-07でログイン。**US-07 は付け替え専用のユーザーなので元に戻さなくてよい**</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>エリア長→経理（会社）に付け替えると担当店舗欄が消える</t>
+          <t>エリア長→経理（会社）に付け替えると担当店舗欄が消える。US-07 を元に戻さないため、以降の検証で US-07 は経理（会社）として扱う</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>S-01 S-05</t>
+          <t>S-01 S-05／**実施前に、別の全権アカウントでログインできることを確認しておく**</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>自ロールから権限設定をなしにして保存を試みる。次にUS-04（店舗）で権限設定のURLを直接開く</t>
+          <t>**別の全権アカウントを用意してから実施する。**自ロールから権限設定をなしにして保存を試みる。次にUS-04（店舗）で権限設定のURLを直接開く</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>無警告で保存できてしまうと自分を締め出せる</t>
+          <t>無警告で保存できてしまうと自分を締め出せる。**もし保存できてしまった場合は、用意した別の全権アカウントで元に戻してから次へ進む**</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>①US-05（閲覧のみ・区分=会社）で会社情報を変更し保存（値が更新されるか）②T-11の合計が3,000,000だったか ③US-02のダッシュボード等に出る指標を数える ④権限の作成・割当の操作ログを確認</t>
+          <t>①US-05（閲覧のみ・区分=会社）で会社情報を変更し保存（値が更新されるか）**→確認後に元の値へ戻す** ②T-11の合計が3,000,000だったか ③US-02のダッシュボード等に出る指標を数える ④権限の作成・割当の操作ログを確認</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">

--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -682,12 +682,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>使う検証データ</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>実際に行う手順。クリックする場所まで書く</t>
+          <t>検証用データセットのどのシートを使うか。データ不要なケースは「—」</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>US-03でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
+          <t>07（US-03）／03_売上／02_従業員</t>
         </is>
       </c>
     </row>
@@ -709,12 +709,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>期待挙動</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>何が起きればよいか（できること）</t>
+          <t>実際に行う手順。クリックする場所まで書く</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>担当2店舗の合計＝3,000,000 になる</t>
+          <t>US-03でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
     </row>
@@ -736,12 +736,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>起きてはいけないこと</t>
+          <t>期待挙動</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>何が出たらNGか（見えてはいけないもの）。権限の検証は「見えないこと」を確かめる場面が多いため独立させている</t>
+          <t>何が起きればよいか（できること）</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>池袋（400万）が混ざらない。池袋三郎の給与80万が出ない</t>
+          <t>担当2店舗の合計＝3,000,000 になる</t>
         </is>
       </c>
     </row>
@@ -763,12 +763,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>合否ライン</t>
+          <t>起きてはいけないこと</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>OK/NGを分ける数値の線。件数・割合・金額で書く</t>
+          <t>何が出たらNGか（見えてはいけないもの）。権限の検証は「見えないこと」を確かめる場面が多いため独立させている</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>集計の合計＝3,000,000。池袋の混入＝0件（7,000,000ならNG）</t>
+          <t>池袋（400万）が混ざらない。池袋三郎の給与80万が出ない</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>計算根拠</t>
+          <t>合否ライン</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>その数値になる理由。計算系のみ。操作系は「—」</t>
+          <t>OK/NGを分ける数値の線。件数・割合・金額で書く</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>渋谷100万＋新宿200万＝300万。池袋400万が入ると700万になる</t>
+          <t>集計の合計＝3,000,000。池袋の混入＝0件（7,000,000ならNG）</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>確認ポイント</t>
+          <t>計算根拠</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>なぜこれを見るのか、どこで間違えやすいか</t>
+          <t>その数値になる理由。計算系のみ。操作系は「—」</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>合計が7,000,000なら全社が見えている＝NG。P3を前倒しする根拠</t>
+          <t>渋谷100万＋新宿200万＝300万。池袋400万が入ると700万になる</t>
         </is>
       </c>
     </row>
@@ -844,22 +844,22 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>スクショファイル名</t>
+          <t>確認ポイント</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>証跡の保存名。検証IDと合わせる</t>
+          <t>なぜこれを見るのか、どこで間違えやすいか</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>実施時</t>
+          <t>作成時</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>T-11</t>
+          <t>合計が7,000,000なら全社が見えている＝NG。P3を前倒しする根拠</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>受入条件ID</t>
+          <t>スクショに写すもの</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>この検証が担保する受入条件。NGならリリース判断に跳ね返る</t>
+          <t>どの画面のどの瞬間を撮るか。何枚必要かも書く</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>AC-10 AC-11 AC-23</t>
+          <t>売上分析の合計＝3,000,000 と、店舗切替に渋谷・新宿だけが並んだ状態（2枚）</t>
         </is>
       </c>
     </row>
@@ -898,22 +898,22 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>遷移フローID</t>
+          <t>スクショファイル名</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>対応する遷移フロー（20260803_09）。NGなら遷移の設計に跳ね返る</t>
+          <t>証跡の保存名。検証IDと合わせる</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>作成時</t>
+          <t>実施時</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>F-14</t>
+          <t>T-11</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ヘルプページの該当箇所</t>
+          <t>受入条件ID</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>顧客に何と説明しているか。NGならヘルプの記述も直す必要がある</t>
+          <t>この検証が担保する受入条件。NGならリリース判断に跳ね返る</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>ケース別のやり方（複数の店舗をまとめて見せたい）／担当店舗を設定する（図2）</t>
+          <t>AC-10 AC-11 AC-23</t>
         </is>
       </c>
     </row>
@@ -952,22 +952,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>実際の値</t>
+          <t>遷移フローID</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>実施して見えた値・挙動をそのまま書く。判断は書かない</t>
+          <t>対応する遷移フロー（20260803_09）。NGなら遷移の設計に跳ね返る</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>実施時</t>
+          <t>作成時</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>合計 3,000,000。池袋は切替に出ず</t>
+          <t>F-14</t>
         </is>
       </c>
     </row>
@@ -979,64 +979,125 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
+          <t>ヘルプページの該当箇所</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>顧客に何と説明しているか。NGならヘルプの記述も直す必要がある</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>作成時</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（複数の店舗をまとめて見せたい）／担当店舗を設定する（図2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>実際の値</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>実施して見えた値・挙動をそのまま書く。判断は書かない</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>実施時</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>合計 3,000,000。池袋は切替に出ず</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>OK／NG／検証不能。データを投入できない場合は「検証不能」。「問題なし」と書かない</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>実施時</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>■ 使い方</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>1. 「画面」を開き、「前提・入力値」が済んでいることを確かめる</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>2. 「操作」のとおりに操作する</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>3. 「期待挙動」と「起きてはいけないこと」の両方を見る</t>
+          <t>1. 「画面」を開き、「前提・入力値」が済んでいることを確かめる</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>4. 「合否ライン」に照らして「実際の値」と「判定」を書く</t>
+          <t>2. 「操作」のとおりに操作する</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>5. NG のときは「受入条件ID」「遷移フローID」「ヘルプページの該当箇所」を見て、どこに跳ね返るかを確認する</t>
+          <t>3. 「期待挙動」と「起きてはいけないこと」の両方を見る</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>4. 「合否ライン」に照らして「実際の値」と「判定」を書く</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>5. 「スクショに写すもの」のとおり撮り、「スクショファイル名」で保存する</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>6. NG のときは「受入条件ID」「遷移フローID」「ヘルプページの該当箇所」を見て、どこに跳ね返るかを確認する</t>
         </is>
       </c>
     </row>
@@ -1051,26 +1112,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="32" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="38" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1110,66 +1173,76 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>使う検証データ</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>期待挙動</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>起きてはいけないこと</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>合否ライン</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>計算根拠</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>確認ポイント</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>スクショに写すもの</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>スクショファイル名</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>受入条件ID</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>遷移フローID</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>ヘルプページの該当箇所</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>実際の値</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="120" customHeight="1">
+    <row r="3" ht="124" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>準備</t>
@@ -1197,58 +1270,68 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
+          <t>—（データ不要）</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
           <t>ステージングURL（＝________）を開く。仕様モック https://suguru789987.github.io/rakmy-permission-mock/ も開き build版数が最新か確認。仕様書05 §8-6の確認事項をエンジニアに聞く</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>両方が開ける。エンジニアへの確認事項に回答がある</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
           <t>両方開ける＝2/2。確認事項の未回答＝0件</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
           <t>本番 rakmy／rakmy_server に触れていないこと</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>ステージングの権限一覧と仕様モックを並べた状態</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
           <t>—（環境確認）</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4" ht="120" customHeight="1">
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="124" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>準備</t>
@@ -1276,58 +1359,68 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
+          <t>01_店舗／03_売上／04_仕入／05_人件費／06_費用_予算</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>20260803_10 の dataset/01〜06 を投入（店舗3件、売上1:2:4＝100万/200万/400万、仕入・人件費・従業員4名・費用・予算）</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>3店舗と当月1日分の実績が登録済み</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
           <t>3店舗×5種の実績が登録済み。比率 1：2：4 が崩れていない</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>1：2：4。合計からどの店舗が含まれるか一意に逆算できる</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>金額の比率 1：2：4 を崩さない</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>投入後の売上一覧。3店舗の金額が 100万／200万／400万 になっていること</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>S-02</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
           <t>—（データ投入）</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="120" customHeight="1">
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="124" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>準備</t>
@@ -1355,58 +1448,68 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
+          <t>07_検証ユーザー</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
           <t>dataset/07 の US-01〜07 を登録</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>検証ユーザー8名が登録済み</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
           <t>8名が登録済み</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
           <t>メールは +pm01〜08 で区別する</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>登録後のユーザー一覧。US-01〜US-08 の8名が並んだ状態</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>S-03</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
           <t>—（ユーザーの登録）</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="120" customHeight="1">
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="124" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>設定（S-04より前）</t>
@@ -1434,58 +1537,68 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
+          <t>—（権限を作る前のため不要）</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
           <t>権限テンプレート画面で選択途中に「一時保存」→離れて再訪→次に「下書きを破棄」→「適用」</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>一時保存した選択が再訪で復元。適用で権限一覧に登録</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>権限を作成済みの状態で実施して「画面が出ない＝NG」と誤判定しない</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>一時保存の復元＝一致。破棄で既定に戻る。適用で権限一覧に4権限が登録</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
           <t>導入時に顧客が最初に触れる画面。権限を作った後だとこの画面が出ないため、必ず S-04 より前に実施する</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>権限テンプレート画面の全体。4権限の選択欄と「適用」「一時保存」「下書きを破棄」が写っていること</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>AC-33</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>F-01 F-02 F-25</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>導入時の初期設定</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7" ht="120" customHeight="1">
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7" ht="124" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>準備</t>
@@ -1513,58 +1626,68 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
+          <t>08_権限設定値</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
           <t>dataset/08 のとおり作成（経理担当（会社）・経理担当（店舗）・人事担当・エリア長・バイトリーダー・閲覧のみ・スタッフ の7権限）。**エリア長は既定テンプレートに無い＝店長を雛形に選び、権限名を『検証_エリア長』に変えて作る**（顧客が実際に行うカスタマイズの再現）。保存後に再度開いて設定が再現するか確認</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>7権限が保存でき、再表示で設定が再現する</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>欠落・反転が起きない</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>7権限が保存でき、再表示で欠落・反転＝0件</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
           <t>保存が壊れると以降の検証がすべて無意味になる</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>作成後の権限一覧。7権限が並んだ状態</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>S-04</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>AC-07</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>F-03</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>ケース別のやり方</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="120" customHeight="1">
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="124" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>準備</t>
@@ -1592,58 +1715,68 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
+          <t>07_検証ユーザー</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
           <t>dataset/07 のとおり割当（US-01=経理（会社）／US-08=経理（店舗）全店／US-03=渋谷・新宿／US-04・US-06=渋谷／US-07は付け替え用）</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>全員に割当が保存され、店舗の権限に担当店舗が付く</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>会社の権限に担当店舗欄が出ない</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>8名すべてに割当が保存。店舗の権限の担当店舗が未設定＝0件</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
           <t>US-08 は担当店舗＝全店</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>ユーザー割当の一覧。8名すべてに権限が付き、店舗の権限に担当店舗が入っていること</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>AC-14 AC-16</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>F-11 F-14</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>権限をメンバーに割り当てる／担当店舗を設定する</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9" ht="120" customHeight="1">
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9" ht="124" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>準備</t>
@@ -1671,58 +1804,68 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
+          <t>—（プリセット適用前）</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
           <t>プリセット適用前に master／manager／shop_manager でログインし全メニューをスクショ</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>master／manager／shop_manager の3権限分のスクショを取得</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
           <t>3権限分のスクショを取得＝3/3</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
           <t>リリース前にしか取れない。最優先</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>master／manager／shop_manager それぞれのメニュー全体（3枚）。リリース前にしか撮れない</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>S-06×3</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>AC-01</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>—（移植前の記録）</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="120" customHeight="1">
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="124" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>設定</t>
@@ -1750,58 +1893,68 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
           <t>新規作成を開き入力項目を記録。雛形（ベース）の候補を確認。ヘッダーで新規導入デモ／運用デモを切り替える</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>雛形の候補に移植プリセットと「まっさら（なし）」が出る。運用デモでは「既存権限をコピー」が増える</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>雛形の候補に「エリア長」が出ない（既定テンプレートではないため）</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>雛形の候補＝4種＋まっさら（なし）。エリア長は含まれない</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
           <t>項目名を記録（仕様=権限名/区分、実装=キー/ロール名/種別）。UI変更依頼の根拠になる</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>権限編集の基本情報。項目名（キー／ロール名／種別）と雛形プルダウンを開いた状態</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>T-01</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>AC-08</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>F-03 F-26</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>権限を作成する STEP 2　雛形を選ぶ／STEP 3　権限名と区分を決める</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11" ht="120" customHeight="1">
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11" ht="124" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>設定</t>
@@ -1829,58 +1982,68 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
+          <t>—（この検証で作った権限は後で削除）</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
           <t>雛形＝「まっさら（なし）」を選び許可数を確認。既存と同じキーで保存、キー空欄でも保存。新規画面追加時の既定値をエンジニアに確認。**確認後、この検証で作った権限は必ず削除する**</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>「まっさら（なし）」を選ぶと許可0件</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>キーの重複が保存できてしまう。**検証で作った権限を残したまま次に進まない（T-05／T-06 の件数が合わなくなる）**</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>まっさらの許可＝0件。キー重複＝エラー。新規画面の既定＝なし（例外0件）</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
           <t>既定が許可側だと画面が増えるたび全員に見えてしまう</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>「まっさら（なし）」選択直後の権限内容（許可0件）と、キー重複時のエラー表示</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>T-02</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>AC-09 AC-12</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>権限を作成する STEP 2（まっさら（なし））／よくあるご質問（新しい画面が追加された場合）</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="120" customHeight="1">
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12" ht="124" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>設定</t>
@@ -1908,58 +2071,68 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
           <t>新規作成で区分を会社→店舗に切替。それぞれ全展開してカテゴリ数を数える</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>区分=会社で21カテゴリ、区分=店舗で23カテゴリ</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>会社で店舗専用6が出ない／店舗で会社専用4が出ない</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>会社＝21カテゴリ／店舗＝23カテゴリ。総数27カテゴリ53機能</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>共通17 ＋ 会社4 ＝ 21／共通17 ＋ 店舗6 ＝ 23。総数27カテゴリ53機能</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>総数27カテゴリ53機能。数え間違いに注意</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>区分＝会社と区分＝店舗を並べた2枚。それぞれカテゴリ数が数えられる状態</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>T-03</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>AC-05 AC-06</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>F-21</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>権限を作成する STEP 3（図3 会社と店舗の区分）</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13" ht="120" customHeight="1">
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13" ht="124" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>一覧・遷移</t>
@@ -1987,58 +2160,68 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
+          <t>08_権限設定値（許可数の突合）</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
           <t>**7権限すべての**一覧タブ／設定タブの内訳を数える。表示ロール・権限列設定を変更→離れて再訪</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>7権限すべてで一覧の許可数＝実際の設定。列選択が次回も保持（スコープ別）</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>不一致が0件</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>7権限すべてで許可数の不一致＝0件。列選択が次回も一致（スコープ別）</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>許可数＝dataset/08 の「なし」以外の行数。閲覧タブ7項目・設定タブ14項目で数える</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>数値例＝経理(会社)閲覧4/7・設定3／人事 閲覧2/7／バイトL 閲覧1/7／閲覧のみ 閲覧7/7・設定14</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>権限一覧の閲覧タブと設定タブ（2枚）。7権限の許可数が読める状態</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>T-05</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>AC-20 AC-31</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>F-22</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>設定内容を確認する（権限一覧）</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14" ht="120" customHeight="1">
+      <c r="R13" s="4" t="inlineStr"/>
+      <c r="S13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="124" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>一覧・遷移</t>
@@ -2066,58 +2249,68 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
+          <t>07_検証ユーザー（人数の突合）</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
           <t>役割サマリの「割当ユーザー N名」と実保持者数を突合。「割当へ →」を選択</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>7権限すべてで表示人数＝実保持者数。保持者だけに絞り込まれる</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>差分が0件</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>7権限すべてで 表示人数＝実保持者数（差分0）</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>表示人数＝dataset/07 でその権限を割り当てたユーザーの件数</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>保持者0名なら絞り込まず全件＋案内バナー</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>役割サマリ全体。権限ごとの割当人数が読める状態</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>T-06</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>AC-28</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>F-12</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>設定内容を確認する（役割サマリ）／権限をメンバーに割り当てる 方法3</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15" ht="120" customHeight="1">
+      <c r="R14" s="4" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15" ht="124" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>一覧・遷移</t>
@@ -2145,58 +2338,68 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
           <t>一覧の行／一覧のマス目／役割サマリ／割当編集 の4か所から権限編集に入り、保存して着地を確認。あわせて割当編集の「＋権限を新規作成」も</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>4入口とも保存後に来た元へ戻る。マス目からは該当箇所へ移動＋ハイライト</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>入口と違う画面に着地しない。マス目から入ったときに該当箇所が開かず先頭に戻る、ということが起きない</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>4入口すべてで来た元に戻る＝4/4。マス目からの移動＋ハイライトあり</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
           <t>割当編集からの新規作成はベースが「まっさら（なし）」既定</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>4入口それぞれの保存後の着地画面（4枚）。マス目からはハイライトされた箇所</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>T-07</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>AC-27</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>F-04 F-06 F-07 F-08 F-09</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>作成した権限を修正する（入口の一覧表）</t>
         </is>
       </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16" ht="120" customHeight="1">
+      <c r="R15" s="4" t="inlineStr"/>
+      <c r="S15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="124" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>一覧・遷移</t>
@@ -2224,58 +2427,68 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
           <t>検証_エリア長（店長ベースで作成）から売上分析をオフにして保存→US-03のセッションで画面遷移→確認後に元へ戻す</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>設定変更後、次の画面遷移または再ログインで反映される</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>無反映が0件</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>無反映＝0件。即時か再ログインかを記録</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
           <t>即時か再ログインかを必ず記録する（ヘルプの記載と揃える）</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>設定変更後、US-03の画面が切り替わった瞬間（変更前後の2枚）</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>AC-21</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>F-06</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>よくあるご質問（設定した権限はいつから反映されますか）</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17" ht="120" customHeight="1">
+      <c r="R16" s="4" t="inlineStr"/>
+      <c r="S16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17" ht="124" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>権限が効くか</t>
@@ -2303,58 +2516,68 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
+          <t>07（US-01）／08（経理・会社）</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
           <t>US-01（経理・区分=会社）でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>売上分析・仕入分析・詳細分析・集計・お支払いの5画面が開ける</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>従業員管理・従業員（閲覧）・権限設定がメニューに出ず、直URLでも開けない</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>開ける5画面＝100%。開けない3画面＝100%（メニュー非表示かつ直URLも塞ぐ）</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
           <t>費用設定・予算設定は店舗画面のため会社スコープに存在しない</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>開けた5画面のいずれかと、開けない画面の直URLアクセス結果（2枚）</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>T-09</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>AC-10 AC-11</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>F-11</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>ケース別のやり方（経理担当に、売上とお支払だけ見せたい）</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="120" customHeight="1">
+      <c r="R17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="124" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>権限が効くか</t>
@@ -2382,58 +2605,68 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
+          <t>07（US-08）／08（経理・店舗）</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
           <t>US-08（経理・区分=店舗／担当店舗=全店）でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>売上分析・仕入分析・詳細分析・集計・費用設定・予算設定の6画面が開け、3店舗すべてのデータが見える</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>従業員管理・従業員（閲覧）・権限設定が開けない</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>開ける6画面＝100%かつ3店舗すべてのデータが見える。開けない3画面＝100%</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
           <t>お支払いは会社画面のため店舗スコープに存在しない</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>開けた6画面のいずれかと、3店舗すべてのデータが出ている集計画面（2枚）</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>T-09b</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>AC-10 AC-11 AC-16</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>F-11</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>ケース別のやり方（経理担当に、売上とお支払だけ見せたい ＋ 会社と店舗の両方の画面を使わせたい）</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19" ht="120" customHeight="1">
+      <c r="R18" s="4" t="inlineStr"/>
+      <c r="S18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19" ht="124" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>権限が効くか</t>
@@ -2461,58 +2694,68 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
+          <t>07（US-02）／08（人事）／03_売上</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
           <t>US-02 人事でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>従業員情報と締め管理が見える</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>売上分析・仕入分析・詳細分析・集計・お支払いが開けない。ダッシュボードに売上が出ない</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>開ける画面＝従業員関連のみ。売上系5画面＝0件。ダッシュボードに売上が出ない</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
           <t>データが空だと「塞げている」のか区別できない。S-02 の投入が前提</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>人事のダッシュボード。売上の数字が出ていないこと</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>T-10</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>AC-10 AC-11</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>F-11</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>ケース別のやり方（人事担当に、従業員情報だけ見せたい）</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20" ht="120" customHeight="1">
+      <c r="R19" s="4" t="inlineStr"/>
+      <c r="S19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="124" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>権限が効くか</t>
@@ -2540,58 +2783,68 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
+          <t>07（US-03）／03_売上／02_従業員</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
           <t>US-03 検証_エリア長でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>担当2店舗の合計＝3,000,000 になる</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>池袋（400万）が混ざらない。池袋三郎の給与80万が出ない</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>集計の合計＝3,000,000。池袋の混入＝0件（7,000,000ならNG）。給与80万の表示＝0件</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>渋谷100万＋新宿200万＝300万。池袋400万が入ると700万になるため、合計を見れば混入を特定できる</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>合計が7,000,000なら全社が見えている＝NG。P3を前倒しする根拠</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>売上分析の合計＝3,000,000 と、店舗切替に渋谷・新宿だけが並んだ状態（2枚）</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>T-11</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>AC-10 AC-11 AC-23</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>F-14</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>ケース別のやり方（複数の店舗をまとめて見せたい）／担当店舗を設定する（図2）</t>
         </is>
       </c>
-      <c r="P20" s="4" t="inlineStr"/>
-      <c r="Q20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21" ht="120" customHeight="1">
+      <c r="R20" s="4" t="inlineStr"/>
+      <c r="S20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="124" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>権限が効くか</t>
@@ -2619,58 +2872,68 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
+          <t>07（US-04）／04_仕入</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
           <t>US-04 バイトLでログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>売上と日々の入力画面が開ける</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>仕入分析・詳細分析・従業員管理・締め管理・費用設定・予算設定が開けない。原価率が出ない</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>開ける16画面＝100%。開けない7画面＝0件。原価率の表示＝0件</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>率を揃えているため、値の妥当性ではなく「原価率」という項目の有無だけを見る</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>原価率は全店10%に揃えてある。項目の有無だけを見る</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>バイトリーダーの売上分析。原価率の項目が無いこと</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>T-12</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>AC-10 AC-11</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>F-11</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>ケース別のやり方（アルバイトリーダーに、一部の画面だけ見せたい）</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22" ht="120" customHeight="1">
+      <c r="R21" s="4" t="inlineStr"/>
+      <c r="S21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="124" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>権限が効くか</t>
@@ -2698,58 +2961,68 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
+          <t>07（US-05）／06_費用_予算</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
           <t>US-05 閲覧のみでログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>会社スコープの全21画面が開ける</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>—（更新できてしまうかは T-23 で記録）</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>会社スコープの21画面が開ける＝100%</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
           <t>費用設定など店舗専用画面は会社スコープに存在しない</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>会社スコープのメニュー全体。21画面が並んだ状態</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>T-13</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>AC-10 AC-11</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>F-11</t>
         </is>
       </c>
-      <c r="O22" s="4" t="inlineStr">
+      <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>権限を作成する STEP 4（「閲覧」と「操作」は、今回のリリースではどちらも）</t>
         </is>
       </c>
-      <c r="P22" s="4" t="inlineStr"/>
-      <c r="Q22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23" ht="120" customHeight="1">
+      <c r="R22" s="4" t="inlineStr"/>
+      <c r="S22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="124" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>権限が効くか</t>
@@ -2777,58 +3050,68 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
+          <t>07（US-06）</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
           <t>US-06 スタッフでログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>ログインでき、ダッシュボードに着地する</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>ダッシュボード以外が開けない</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>ログインでき、開ける画面＝1（ダッシュボードのみ）。空白・エラー・ループ＝0件</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
           <t>空白・エラー・ループが0件。最小権限でも締め出さない</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>ログイン直後のダッシュボード。他のメニューが出ていないこと</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>T-14</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>AC-10 AC-11 AC-13</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>F-11</t>
         </is>
       </c>
-      <c r="O23" s="4" t="inlineStr">
+      <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>ケース別のやり方（新しく入った方には、まず最小限から始めたい）／よくあるご質問（権限を絞りすぎて、何も見えなくなりませんか）</t>
         </is>
       </c>
-      <c r="P23" s="4" t="inlineStr"/>
-      <c r="Q23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24" ht="120" customHeight="1">
+      <c r="R23" s="4" t="inlineStr"/>
+      <c r="S23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="124" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>割当</t>
@@ -2856,58 +3139,68 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
+          <t>07（US-07）</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
           <t>US-07（検証_エリア長・店舗）の割当編集で 検証_経理担当（会社）に付け替え、行の表示を確認してから保存→US-07でログイン。**US-07 は付け替え専用のユーザーなので元に戻さなくてよい**</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>別の権限を選んで保存すると前の権限が外れる。行に「選ぶと『◯◯』から置き換わります」が出る</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>権限を2つ同時に選べない</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>同時に選べる権限＝1つ。付け替え後に前の権限の画面＝0件。置換予告の表示＝100%</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
           <t>エリア長→経理（会社）に付け替えると担当店舗欄が消える。US-07 を元に戻さないため、以降の検証で US-07 は経理（会社）として扱う</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>割当編集で置換予告「選ぶと『◯◯』から置き換わります」が出ている状態と、保存後の確認画面（2枚）</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>T-15</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>AC-14 AC-15</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="P24" s="4" t="inlineStr">
         <is>
           <t>F-05 F-10 F-13 F-23</t>
         </is>
       </c>
-      <c r="O24" s="4" t="inlineStr">
+      <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>権限を変更・解除する／権限をメンバーに割り当てる 方法1（すでに別の権限をお持ちの方）</t>
         </is>
       </c>
-      <c r="P24" s="4" t="inlineStr"/>
-      <c r="Q24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25" ht="120" customHeight="1">
+      <c r="R24" s="4" t="inlineStr"/>
+      <c r="S24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25" ht="124" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>割当</t>
@@ -2935,58 +3228,68 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
+          <t>07_検証ユーザー</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
           <t>検証_エリア長（店舗）で一括割当を開く→「すべて表示」</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>店舗の権限では店舗所属、会社の権限では本部所属が表示される。「すべて表示」で解除できる</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>店舗の権限で「含める」にチェックしただけで担当店舗0件のまま保存できない</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>店舗の権限で表示＝店舗所属のみ、会社の権限で表示＝本部所属のみ。「すべて表示」で8名全員が出る。店舗0件での保存＝0件</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
           <t>店舗ロール＆含める＆店舗0件はエラー</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>一括割当の絞り込み前と「すべて表示」後（2枚）</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>T-16</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>AC-15</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>F-10</t>
         </is>
       </c>
-      <c r="O25" s="4" t="inlineStr">
+      <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>権限をメンバーに割り当てる 方法1（対象は自動で絞り込まれます）</t>
         </is>
       </c>
-      <c r="P25" s="4" t="inlineStr"/>
-      <c r="Q25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26" ht="120" customHeight="1">
+      <c r="R25" s="4" t="inlineStr"/>
+      <c r="S25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="124" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>割当</t>
@@ -3014,58 +3317,68 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
           <t>**別の全権アカウントを用意してから実施する。**自ロールから権限設定をなしにして保存を試みる。次にUS-04（店舗）で権限設定のURLを直接開く</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>自ロールから権限設定を外すと警告が出る、または最後の全権は外せない</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>一般の権限で権限設定が開けない</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>無警告で保存できる＝0件。一般の権限で権限設定が開ける＝0件</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
           <t>無警告で保存できてしまうと自分を締め出せる。**もし保存できてしまった場合は、用意した別の全権アカウントで元に戻してから次へ進む**</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>自ロールから権限設定を外そうとしたときの警告表示と、US-04での直URLアクセス結果（2枚）</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>T-17</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>AC-17 AC-18</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="P26" s="4" t="inlineStr">
         <is>
           <t>F-24</t>
         </is>
       </c>
-      <c r="O26" s="4" t="inlineStr">
+      <c r="Q26" s="4" t="inlineStr">
         <is>
           <t>よくあるご質問（自分の権限を変更できますか）</t>
         </is>
       </c>
-      <c r="P26" s="4" t="inlineStr"/>
-      <c r="Q26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27" ht="120" customHeight="1">
+      <c r="R26" s="4" t="inlineStr"/>
+      <c r="S26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27" ht="124" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>割当</t>
@@ -3093,58 +3406,68 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
+          <t>07（US-06）</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
           <t>US-06の割当編集で「割当なし」を選び保存→ログイン確認→S-05に戻す。次に店舗を選ばず店舗の権限を割当して保存</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>「割当なし」で保存すると未割当になり、ログインしても画面が出ない</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>担当店舗0件では保存できない、または警告が出る</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>未割当で開ける画面＝0件。担当店舗0件のまま保存できる＝0件</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
           <t>権限設定画面に「⚠ ◯名が店舗未設定」が出る</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>「割当なし」保存後のユーザー割当（未割当の表示）と、担当店舗0件での保存エラー（2枚）</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>T-18</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>AC-04 AC-19</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="P27" s="4" t="inlineStr">
         <is>
           <t>F-14 F-15</t>
         </is>
       </c>
-      <c r="O27" s="4" t="inlineStr">
+      <c r="Q27" s="4" t="inlineStr">
         <is>
           <t>権限を変更・解除する（権限を外す）／担当店舗を設定する（1つ以上お選びください）</t>
         </is>
       </c>
-      <c r="P27" s="4" t="inlineStr"/>
-      <c r="Q27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28" ht="120" customHeight="1">
+      <c r="R27" s="4" t="inlineStr"/>
+      <c r="S27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="124" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>指標</t>
@@ -3172,58 +3495,68 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
+          <t>09_指標の初期値（期待値の突合）</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
           <t>スタッフ・検証_エリア長・経理の指標一覧を開き、店舗／会社タブのON件数を数える。任意の指標をON/OFF</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>従業員ベース=店舗17/会社0、店長ベース=店舗36/会社8、本部管理ベース=店舗36/会社25</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>保存ボタンが無く、切替はその場で反映される</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>7権限すべてで dataset/09 の値と一致（差分0）。保存ボタン＝なし</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>指標の既定は雛形で決まる。従業員＝openのみON（店舗17/会社0）、店長＝open＋mgr（36/8）、本部管理＝全件（36/25）</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>7権限すべてを dataset/09 の値と突合する</t>
         </is>
       </c>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>7権限それぞれの指標一覧。店舗指標・会社指標のON件数が読める状態</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>T-19</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>AC-25</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>F-16</t>
         </is>
       </c>
-      <c r="O28" s="4" t="inlineStr">
+      <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>表示する数字を選ぶ（初期値は自動で設定されます）</t>
         </is>
       </c>
-      <c r="P28" s="4" t="inlineStr"/>
-      <c r="Q28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29" ht="120" customHeight="1">
+      <c r="R28" s="4" t="inlineStr"/>
+      <c r="S28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29" ht="124" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>指標</t>
@@ -3251,58 +3584,68 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
           <t>指標条件設定で推奨テンプレ「店長向け」を適用（キャンセルとの差も確認）→マイテンプレートに保存→別の権限で読込。次に「👑オーナー操作」の指標管理と付与先指定</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>おすすめの組み合わせを適用でき、名前をつけて保存して他権限で読込できる</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>指標管理に編集UI（トグル/コピー/条件設定）が出ない。オーナー以外が付与先指定を実行できない</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>テンプレ適用の結果が定義と一致。指標管理に編集UI＝0件。オーナー以外の付与先指定＝0件</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
           <t>「適用して指標一覧へ」まで反映されない。キャンセルは非適用</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>指標条件設定の適用前後と、マイテンプレートの保存・読込、👑オーナー操作の指標管理（読取専用であること）</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>T-20</t>
         </is>
       </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>AC-29 AC-30</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="P29" s="4" t="inlineStr">
         <is>
           <t>F-17 F-18 F-19 F-20</t>
         </is>
       </c>
-      <c r="O29" s="4" t="inlineStr">
+      <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>表示する数字を選ぶ（指標条件設定 ＋ マイテンプレート）／オーナーだけができること</t>
         </is>
       </c>
-      <c r="P29" s="4" t="inlineStr"/>
-      <c r="Q29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30" ht="120" customHeight="1">
+      <c r="R29" s="4" t="inlineStr"/>
+      <c r="S29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="124" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>移植</t>
@@ -3330,58 +3673,68 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
+          <t>—（プリセット適用後）</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
           <t>プリセット適用後に master／manager／shop_manager で全メニューを再取得しS-06と突合。ユーザー割当一覧で未割当を数える</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>master／manager／shop_manager と同じ動作のプリセットがある</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>適用前後で見える画面の増減が0</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>3権限とも適用前後で見える画面の増減＝0</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
           <t>S-06 のスクショと1画面ずつ突き合わせる</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>master／manager／shop_manager のメニュー全体（3枚）。S-06 と並べて比較する</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>T-21×3</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>AC-01 AC-02 AC-03 AC-04</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O30" s="4" t="inlineStr">
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>—（現行からの移植。顧客向けの記載なし）</t>
         </is>
       </c>
-      <c r="P30" s="4" t="inlineStr"/>
-      <c r="Q30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31" ht="120" customHeight="1">
+      <c r="R30" s="4" t="inlineStr"/>
+      <c r="S30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31" ht="124" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>設計レビュー</t>
@@ -3409,58 +3762,68 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
+          <t>—（設計レビュー）</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
           <t>エンジニアと画面・APIを一緒に棚卸しし、7点を確認する。①ユーザー個別に権限内容を編集できるUI/APIが無いか ②店舗ロールでも担当店舗を全店・複数店に設定できるか ③権限の状態が なし/閲覧/操作 の3つだけか ④指標一覧に機密度のバッジが出ていないか ⑤店舗ロールの指標一覧で会社指標をONにできるか（既定OFF）⑥一括割当で店舗を選んだだけでは権限が付与されないか ⑦画面カテゴリを新しく追加したとき、既存の全権限で既定が「なし」になるか（AC-12 のコード上の既定値を確認）</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>7点すべてが設計どおり</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>7点のいずれかが設計と違う状態で「画面は動くから問題なし」と判定されない</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>7点すべてが設計どおり（1つでも崩れていればNG）</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
           <t>動くかどうかではなく「そう作られているか」を見る</t>
         </is>
       </c>
-      <c r="L31" s="4" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>エンジニアと確認した7点の記録（画面またはコード箇所）</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>T-24_レビュー記録</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>K-01 K-02 K-03 K-04 K-05 K-06 AC-12</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>F-11 F-14 F-16 F-22</t>
         </is>
       </c>
-      <c r="O31" s="4" t="inlineStr">
+      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>—（設計レビュー。顧客向けの記載なし）</t>
         </is>
       </c>
-      <c r="P31" s="4" t="inlineStr"/>
-      <c r="Q31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32" ht="120" customHeight="1">
+      <c r="R31" s="4" t="inlineStr"/>
+      <c r="S31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32" ht="124" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>判定</t>
@@ -3488,58 +3851,68 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
+          <t>—（これまでの結果を集約）</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
           <t>各シナリオが意図どおり作れたかを判定</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>SC-01a/01b/02/04/06 の5件で ×（作れない）が0件</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>×（作れない）が必須5シナリオに1件でも出ない</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>SC-01a/01b/02/04/06 の5件で ×＝0件</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
           <t>SC-03・SC-05 は P1 では×が想定。判定せず記録する</t>
         </is>
       </c>
-      <c r="L32" s="4" t="inlineStr">
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>不要（判定表に記録）</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>AC-22 AC-32</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>ケース別のやり方（6ケースすべて）</t>
         </is>
       </c>
-      <c r="P32" s="4" t="inlineStr"/>
-      <c r="Q32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33" ht="120" customHeight="1">
+      <c r="R32" s="4" t="inlineStr"/>
+      <c r="S32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33" ht="124" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>次段階</t>
@@ -3567,63 +3940,73 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
+          <t>07／03_売上／09_指標の初期値</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
           <t>①US-05（閲覧のみ・区分=会社）で会社情報を変更し保存（値が更新されるか）**→確認後に元の値へ戻す** ②T-11の合計が3,000,000だったか ③US-02のダッシュボード等に出る指標を数える ④権限の作成・割当の操作ログを確認</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>判定せず実測のみ記録</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>「問題なし」と書かない。実測値をそのまま記録する</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>判定せず実測を記録（①更新可否 ②合計値 ③指標数 ④ログ有無）</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>②の合計が7,000,000なら全社が見えている＝P3が必要という判断根拠になる</t>
         </is>
       </c>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="L33" s="4" t="inlineStr">
         <is>
           <t>①更新できる→P2が必要 ②700万→P3が必要 ③許可外の指標が出る→P4が必要 ④ログが無い→P5が必要</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr">
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>①会社情報の保存結果 ②US-03の合計値 ③US-02に出た指標 ④操作ログ（4枚）</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>T-23</t>
         </is>
       </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>AC-23 AC-24 AC-25 AC-26</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O33" s="4" t="inlineStr">
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>よくあるご質問（画面は見せたいが、変更はさせたくない場合）／担当店舗を設定する（今回のリリースでは、担当店舗は割り当ての記録として保存）</t>
         </is>
       </c>
-      <c r="P33" s="4" t="inlineStr"/>
-      <c r="Q33" s="4" t="inlineStr">
+      <c r="R33" s="4" t="inlineStr"/>
+      <c r="S33" s="4" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="Q3:Q33">
+  <conditionalFormatting sqref="S3:S33">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -3632,7 +4015,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="Q3:Q33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="S3:S33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,検証不能"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -795,7 +795,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>OK/NGを分ける数値の線。件数・割合・金額で書く</t>
+          <t>OK/NGを分ける数値の線。件数・割合・金額で書く。**どの画面で見るかを「画面」列と揃える**</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>集計の合計＝3,000,000。池袋の混入＝0件（7,000,000ならNG）</t>
+          <t>売上分析の合計＝3,000,000。池袋の混入＝0件（7,000,000ならNG）</t>
         </is>
       </c>
     </row>
@@ -1052,52 +1052,140 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>実施者</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>誰が実施したか。証跡として残す</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>実施時</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>鈴木</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>実施日</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>いつ実施したか。実装が変わると結果も変わるため必須</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>実施時</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>NGの詳細、再実施の記録、検証不能の理由など</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>実施時</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>1回目NG。修正後の再実施でOK（8/22）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>■ 使い方</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>1. 「画面」を開き、「前提・入力値」が済んでいることを確かめる</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>2. 「操作」のとおりに操作する</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>3. 「期待挙動」と「起きてはいけないこと」の両方を見る</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>4. 「合否ライン」に照らして「実際の値」と「判定」を書く</t>
+          <t>1. 「画面」を開き、「前提・入力値」が済んでいることを確かめる</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>5. 「スクショに写すもの」のとおり撮り、「スクショファイル名」で保存する</t>
+          <t>2. 「操作」のとおりに操作する</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>6. NG のときは「受入条件ID」「遷移フローID」「ヘルプページの該当箇所」を見て、どこに跳ね返るかを確認する</t>
+          <t>3. 「期待挙動」と「起きてはいけないこと」の両方を見る</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>4. 「合否ライン」に照らして「実際の値」と「判定」を書く</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>5. 「スクショに写すもの」のとおり撮り、「スクショファイル名」で保存する</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>6. 「実施者」「実施日」を記入する（実装が変わると結果も変わるため、いつ誰が確かめたかを残す）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>7. NG のときは「受入条件ID」「遷移フローID」「ヘルプページの該当箇所」を見て、どこに跳ね返るかを確認し、「備考」に詳細を書く</t>
         </is>
       </c>
     </row>
@@ -1112,28 +1200,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="38" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1241,6 +1332,21 @@
           <t>判定</t>
         </is>
       </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>実施者</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>実施日</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="124" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -1260,7 +1366,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>権限設定（ステージング）／仕様モック</t>
+          <t>権限設定（ステージングの権限一覧）／仕様モック</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -1330,6 +1436,9 @@
       </c>
       <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="4" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr"/>
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="124" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -1419,6 +1528,9 @@
       </c>
       <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="124" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1508,6 +1620,9 @@
       </c>
       <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="124" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -1527,7 +1642,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>権限テンプレート（初回表示）</t>
+          <t>権限テンプレート（初回表示）→ 適用後は権限一覧に着地</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1597,6 +1712,9 @@
       </c>
       <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="124" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -1616,7 +1734,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>権限設定 → ＋権限を新規作成</t>
+          <t>権限設定 → ＋権限を新規作成 → 保存後は権限一覧に着地</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1686,6 +1804,9 @@
       </c>
       <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr"/>
+      <c r="U7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="124" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -1775,6 +1896,9 @@
       </c>
       <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr"/>
+      <c r="U8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="124" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -1864,6 +1988,9 @@
       </c>
       <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr"/>
+      <c r="U9" s="4" t="inlineStr"/>
+      <c r="V9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="124" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1953,6 +2080,9 @@
       </c>
       <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="4" t="inlineStr"/>
+      <c r="T10" s="4" t="inlineStr"/>
+      <c r="U10" s="4" t="inlineStr"/>
+      <c r="V10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="124" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -2042,6 +2172,9 @@
       </c>
       <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr"/>
+      <c r="U11" s="4" t="inlineStr"/>
+      <c r="V11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="124" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -2131,6 +2264,9 @@
       </c>
       <c r="R12" s="4" t="inlineStr"/>
       <c r="S12" s="4" t="inlineStr"/>
+      <c r="T12" s="4" t="inlineStr"/>
+      <c r="U12" s="4" t="inlineStr"/>
+      <c r="V12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="124" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -2220,6 +2356,9 @@
       </c>
       <c r="R13" s="4" t="inlineStr"/>
       <c r="S13" s="4" t="inlineStr"/>
+      <c r="T13" s="4" t="inlineStr"/>
+      <c r="U13" s="4" t="inlineStr"/>
+      <c r="V13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="124" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -2309,6 +2448,9 @@
       </c>
       <c r="R14" s="4" t="inlineStr"/>
       <c r="S14" s="4" t="inlineStr"/>
+      <c r="T14" s="4" t="inlineStr"/>
+      <c r="U14" s="4" t="inlineStr"/>
+      <c r="V14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="124" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -2398,6 +2540,9 @@
       </c>
       <c r="R15" s="4" t="inlineStr"/>
       <c r="S15" s="4" t="inlineStr"/>
+      <c r="T15" s="4" t="inlineStr"/>
+      <c r="U15" s="4" t="inlineStr"/>
+      <c r="V15" s="4" t="inlineStr"/>
     </row>
     <row r="16" ht="124" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -2487,6 +2632,9 @@
       </c>
       <c r="R16" s="4" t="inlineStr"/>
       <c r="S16" s="4" t="inlineStr"/>
+      <c r="T16" s="4" t="inlineStr"/>
+      <c r="U16" s="4" t="inlineStr"/>
+      <c r="V16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="124" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -2576,6 +2724,9 @@
       </c>
       <c r="R17" s="4" t="inlineStr"/>
       <c r="S17" s="4" t="inlineStr"/>
+      <c r="T17" s="4" t="inlineStr"/>
+      <c r="U17" s="4" t="inlineStr"/>
+      <c r="V17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="124" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -2665,6 +2816,9 @@
       </c>
       <c r="R18" s="4" t="inlineStr"/>
       <c r="S18" s="4" t="inlineStr"/>
+      <c r="T18" s="4" t="inlineStr"/>
+      <c r="U18" s="4" t="inlineStr"/>
+      <c r="V18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="124" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -2754,6 +2908,9 @@
       </c>
       <c r="R19" s="4" t="inlineStr"/>
       <c r="S19" s="4" t="inlineStr"/>
+      <c r="T19" s="4" t="inlineStr"/>
+      <c r="U19" s="4" t="inlineStr"/>
+      <c r="V19" s="4" t="inlineStr"/>
     </row>
     <row r="20" ht="124" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -2773,7 +2930,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>US-03でログイン → 売上分析・従業員管理</t>
+          <t>US-03でログイン → 売上分析（合計を見る）／集計／従業員管理</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -2803,7 +2960,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>集計の合計＝3,000,000。池袋の混入＝0件（7,000,000ならNG）。給与80万の表示＝0件</t>
+          <t>**売上分析の合計＝3,000,000**（集計画面でも同額）。池袋の混入＝0件（7,000,000ならNG）。給与80万の表示＝0件</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -2818,7 +2975,7 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>売上分析の合計＝3,000,000 と、店舗切替に渋谷・新宿だけが並んだ状態（2枚）</t>
+          <t>売上分析の合計＝3,000,000 と、店舗切替に渋谷・新宿だけが並んだ状態（2枚）。集計画面でも同額であることを確認</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -2843,6 +3000,9 @@
       </c>
       <c r="R20" s="4" t="inlineStr"/>
       <c r="S20" s="4" t="inlineStr"/>
+      <c r="T20" s="4" t="inlineStr"/>
+      <c r="U20" s="4" t="inlineStr"/>
+      <c r="V20" s="4" t="inlineStr"/>
     </row>
     <row r="21" ht="124" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -2932,6 +3092,9 @@
       </c>
       <c r="R21" s="4" t="inlineStr"/>
       <c r="S21" s="4" t="inlineStr"/>
+      <c r="T21" s="4" t="inlineStr"/>
+      <c r="U21" s="4" t="inlineStr"/>
+      <c r="V21" s="4" t="inlineStr"/>
     </row>
     <row r="22" ht="124" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -3021,6 +3184,9 @@
       </c>
       <c r="R22" s="4" t="inlineStr"/>
       <c r="S22" s="4" t="inlineStr"/>
+      <c r="T22" s="4" t="inlineStr"/>
+      <c r="U22" s="4" t="inlineStr"/>
+      <c r="V22" s="4" t="inlineStr"/>
     </row>
     <row r="23" ht="124" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -3040,7 +3206,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>US-06でログイン → ログイン直後</t>
+          <t>US-06でログイン → ログイン直後のダッシュボード</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -3110,6 +3276,9 @@
       </c>
       <c r="R23" s="4" t="inlineStr"/>
       <c r="S23" s="4" t="inlineStr"/>
+      <c r="T23" s="4" t="inlineStr"/>
+      <c r="U23" s="4" t="inlineStr"/>
+      <c r="V23" s="4" t="inlineStr"/>
     </row>
     <row r="24" ht="124" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -3129,7 +3298,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>ユーザー割当 → 割当を編集</t>
+          <t>ユーザー割当 → 割当を編集（＝割当編集）</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -3199,6 +3368,9 @@
       </c>
       <c r="R24" s="4" t="inlineStr"/>
       <c r="S24" s="4" t="inlineStr"/>
+      <c r="T24" s="4" t="inlineStr"/>
+      <c r="U24" s="4" t="inlineStr"/>
+      <c r="V24" s="4" t="inlineStr"/>
     </row>
     <row r="25" ht="124" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -3288,6 +3460,9 @@
       </c>
       <c r="R25" s="4" t="inlineStr"/>
       <c r="S25" s="4" t="inlineStr"/>
+      <c r="T25" s="4" t="inlineStr"/>
+      <c r="U25" s="4" t="inlineStr"/>
+      <c r="V25" s="4" t="inlineStr"/>
     </row>
     <row r="26" ht="124" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -3377,6 +3552,9 @@
       </c>
       <c r="R26" s="4" t="inlineStr"/>
       <c r="S26" s="4" t="inlineStr"/>
+      <c r="T26" s="4" t="inlineStr"/>
+      <c r="U26" s="4" t="inlineStr"/>
+      <c r="V26" s="4" t="inlineStr"/>
     </row>
     <row r="27" ht="124" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -3466,6 +3644,9 @@
       </c>
       <c r="R27" s="4" t="inlineStr"/>
       <c r="S27" s="4" t="inlineStr"/>
+      <c r="T27" s="4" t="inlineStr"/>
+      <c r="U27" s="4" t="inlineStr"/>
+      <c r="V27" s="4" t="inlineStr"/>
     </row>
     <row r="28" ht="124" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -3555,6 +3736,9 @@
       </c>
       <c r="R28" s="4" t="inlineStr"/>
       <c r="S28" s="4" t="inlineStr"/>
+      <c r="T28" s="4" t="inlineStr"/>
+      <c r="U28" s="4" t="inlineStr"/>
+      <c r="V28" s="4" t="inlineStr"/>
     </row>
     <row r="29" ht="124" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -3644,6 +3828,9 @@
       </c>
       <c r="R29" s="4" t="inlineStr"/>
       <c r="S29" s="4" t="inlineStr"/>
+      <c r="T29" s="4" t="inlineStr"/>
+      <c r="U29" s="4" t="inlineStr"/>
+      <c r="V29" s="4" t="inlineStr"/>
     </row>
     <row r="30" ht="124" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -3733,6 +3920,9 @@
       </c>
       <c r="R30" s="4" t="inlineStr"/>
       <c r="S30" s="4" t="inlineStr"/>
+      <c r="T30" s="4" t="inlineStr"/>
+      <c r="U30" s="4" t="inlineStr"/>
+      <c r="V30" s="4" t="inlineStr"/>
     </row>
     <row r="31" ht="124" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -3822,6 +4012,9 @@
       </c>
       <c r="R31" s="4" t="inlineStr"/>
       <c r="S31" s="4" t="inlineStr"/>
+      <c r="T31" s="4" t="inlineStr"/>
+      <c r="U31" s="4" t="inlineStr"/>
+      <c r="V31" s="4" t="inlineStr"/>
     </row>
     <row r="32" ht="124" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -3911,6 +4104,9 @@
       </c>
       <c r="R32" s="4" t="inlineStr"/>
       <c r="S32" s="4" t="inlineStr"/>
+      <c r="T32" s="4" t="inlineStr"/>
+      <c r="U32" s="4" t="inlineStr"/>
+      <c r="V32" s="4" t="inlineStr"/>
     </row>
     <row r="33" ht="124" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -4004,6 +4200,9 @@
           <t>対象外</t>
         </is>
       </c>
+      <c r="T33" s="4" t="inlineStr"/>
+      <c r="U33" s="4" t="inlineStr"/>
+      <c r="V33" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="S3:S33">

--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>AC-01</t>
+          <t>AC-01 AC-02 AC-03</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>AC-10 AC-11 AC-23</t>
+          <t>AC-10 AC-11 AC-16 AC-23</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>AC-23 AC-24 AC-25 AC-26</t>
+          <t>AC-23 AC-24 AC-25 AC-26 AC-32</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">

--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -2535,7 +2535,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>作成した権限を修正する（入口の一覧表）</t>
+          <t>作成した権限を修正する（どこから入っても同じ編集画面）</t>
         </is>
       </c>
       <c r="R15" s="4" t="inlineStr"/>

--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V33"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3927,52 +3927,52 @@
     <row r="31" ht="124" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>設計レビュー</t>
+          <t>事故防止</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>T-24</t>
+          <t>T-25</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>境界設計の確認（動作テストでは検出できない）</t>
+          <t>割当済みの権限を削除しようとしたとき</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>エンジニアと画面・APIを一緒に棚卸し</t>
+          <t>権限一覧（削除ボタン）→ 割当を外してから再度削除</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>S-01</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>—（設計レビュー）</t>
+          <t>07（US-04）／08（バイトリーダー）</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>エンジニアと画面・APIを一緒に棚卸しし、7点を確認する。①ユーザー個別に権限内容を編集できるUI/APIが無いか ②店舗ロールでも担当店舗を全店・複数店に設定できるか ③権限の状態が なし/閲覧/操作 の3つだけか ④指標一覧に機密度のバッジが出ていないか ⑤店舗ロールの指標一覧で会社指標をONにできるか（既定OFF）⑥一括割当で店舗を選んだだけでは権限が付与されないか ⑦画面カテゴリを新しく追加したとき、既存の全権限で既定が「なし」になるか（AC-12 のコード上の既定値を確認）</t>
+          <t>割当ユーザーが1名以上いる権限（検証_バイトリーダー）で削除を実行する→警告を確認→ユーザー割当でその人の割当を外す→再度削除する</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>7点すべてが設計どおり</t>
+          <t>割当がある間は警告が出て削除されない。割当を外すと削除できる</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>7点のいずれかが設計と違う状態で「画面は動くから問題なし」と判定されない</t>
+          <t>無警告で削除されて、その人が未割当になる</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>7点すべてが設計どおり（1つでも崩れていればNG）</t>
+          <t>割当1名以上での削除がブロックされる＝100%。無警告で削除できる＝0件。割当0名なら削除できる</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -3982,32 +3982,32 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>動くかどうかではなく「そう作られているか」を見る</t>
+          <t>権限を消した瞬間に未割当が発生すると AC-04（未割当0名）と衝突する。業務停止に直結する</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>エンジニアと確認した7点の記録（画面またはコード箇所）</t>
+          <t>削除実行時の警告表示と、割当を外したあとに削除できた権限一覧（2枚）</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>T-24_レビュー記録</t>
+          <t>T-25</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>K-01 K-02 K-03 K-04 K-05 K-06 AC-12</t>
+          <t>AC-35 AC-04</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>F-11 F-14 F-16 F-22</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>—（設計レビュー。顧客向けの記載なし）</t>
+          <t>作成した権限を修正する（権限を削除する）</t>
         </is>
       </c>
       <c r="R31" s="4" t="inlineStr"/>
@@ -4019,52 +4019,52 @@
     <row r="32" ht="124" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>判定</t>
+          <t>割当</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>T-22</t>
+          <t>T-26</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>7シナリオの意図判定</t>
+          <t>「全店」と店舗の増減</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>これまでの結果をまとめて判定</t>
+          <t>店舗管理（店舗を追加・閉店）→ 割当編集（対象店舗）→ US-08でログイン</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>T-09〜T-14 T-20</t>
+          <t>S-05／入力値：US-08＝全店</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>—（これまでの結果を集約）</t>
+          <t>01_店舗／07（US-08）</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>各シナリオが意図どおり作れたかを判定</t>
+          <t>店舗を1件追加する→US-08の割当編集を開いて対象店舗を確認→US-08でログインして新店舗のデータが見えるか確認。次に1店舗を閉店にして、担当店舗の紐付けが残るか確認</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>SC-01a/01b/02/04/06 の5件で ×（作れない）が0件</t>
+          <t>店舗を追加すると「全店」の人の対象に自動で含まれる。閉店にしても担当店舗の紐付けは消えない</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>×（作れない）が必須5シナリオに1件でも出ない</t>
+          <t>全店の人が再設定しないと新店舗を見られない。閉店で担当店舗が0件になる</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>SC-01a/01b/02/04/06 の5件で ×＝0件</t>
+          <t>新店舗が自動で対象に含まれる＝100%。再設定が必要＝0件。閉店後に担当店舗0件になる人＝0名</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -4074,32 +4074,32 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>SC-03・SC-05 は P1 では×が想定。判定せず記録する</t>
+          <t>動的にすると閲覧範囲が黙って広がる。ヘルプに明示しているか併せて確認する</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>不要（判定表に記録）</t>
+          <t>店舗追加後のUS-08の対象店舗と、US-08でログインしたときの店舗切替（2枚）</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>T-26</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>AC-22 AC-32</t>
+          <t>AC-36 AC-37</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-14</t>
         </is>
       </c>
       <c r="Q32" s="4" t="inlineStr">
         <is>
-          <t>ケース別のやり方（6ケースすべて）</t>
+          <t>担当店舗を設定する（担当店舗は複数選択できます）</t>
         </is>
       </c>
       <c r="R32" s="4" t="inlineStr"/>
@@ -4111,101 +4111,377 @@
     <row r="33" ht="124" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>次段階</t>
+          <t>設定</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>T-23</t>
+          <t>T-27</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>対象外4項目の実測</t>
+          <t>権限名の重複と区分の変更</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>US-05で会社情報／US-03の合計／US-02の指標／操作ログ</t>
+          <t>権限編集（基本情報）</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>S-05 T-11／入力値：US-05／US-03／US-02／操作ログ</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>07／03_売上／09_指標の初期値</t>
+          <t>08_権限設定値</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>①US-05（閲覧のみ・区分=会社）で会社情報を変更し保存（値が更新されるか）**→確認後に元の値へ戻す** ②T-11の合計が3,000,000だったか ③US-02のダッシュボード等に出る指標を数える ④権限の作成・割当の操作ログを確認</t>
+          <t>既存と同じ権限名（検証_人事担当）で新規作成し保存を試みる→別名に直して保存。次に既存の権限を開いて区分を変更できるか確認する</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>判定せず実測のみ記録</t>
+          <t>重複した名前では保存できず「別名で保存してください」が出る。別名にすれば保存できる。既存権限の区分は変更できない</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>「問題なし」と書かない。実測値をそのまま記録する</t>
+          <t>同じ権限名が2つ並ぶ。区分を変更できてしまい設定値が意味を失う</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>判定せず実測を記録（①更新可否 ②合計値 ③指標数 ④ログ有無）</t>
+          <t>重複名での保存＝0件。別名での保存＝成功。編集時に区分が変更できる＝0件</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>②の合計が7,000,000なら全社が見えている＝P3が必要という判断根拠になる</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>①更新できる→P2が必要 ②700万→P3が必要 ③許可外の指標が出る→P4が必要 ④ログが無い→P5が必要</t>
+          <t>区分を変えたい場合は新規作成に誘導されるか。誘導が無ければ顧客が迷う</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>①会社情報の保存結果 ②US-03の合計値 ③US-02に出た指標 ④操作ログ（4枚）</t>
+          <t>重複名でのエラーメッセージと、編集画面で区分が変更できない状態（2枚）</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>T-23</t>
+          <t>T-27</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>AC-23 AC-24 AC-25 AC-26 AC-32</t>
+          <t>AC-38 AC-39</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-03 F-06</t>
         </is>
       </c>
       <c r="Q33" s="4" t="inlineStr">
         <is>
-          <t>よくあるご質問（画面は見せたいが、変更はさせたくない場合）／担当店舗を設定する（今回のリリースでは、担当店舗は割り当ての記録として保存）</t>
+          <t>権限を作成する STEP 3　権限名と区分を決める</t>
         </is>
       </c>
       <c r="R33" s="4" t="inlineStr"/>
-      <c r="S33" s="4" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
+      <c r="S33" s="4" t="inlineStr"/>
       <c r="T33" s="4" t="inlineStr"/>
       <c r="U33" s="4" t="inlineStr"/>
       <c r="V33" s="4" t="inlineStr"/>
     </row>
+    <row r="34" ht="124" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>設計レビュー</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>T-24</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>境界設計の確認（動作テストでは検出できない）</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>エンジニアと画面・APIを一緒に棚卸し</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>S-01</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>—（設計レビュー）</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>エンジニアと画面・APIを一緒に棚卸しし、7点を確認する。①ユーザー個別に権限内容を編集できるUI/APIが無いか ②店舗ロールでも担当店舗を全店・複数店に設定できるか ③権限の状態が なし/閲覧/操作 の3つだけか ④指標一覧に機密度のバッジが出ていないか ⑤店舗ロールの指標一覧で会社指標をONにできるか（既定OFF）⑥一括割当で店舗を選んだだけでは権限が付与されないか ⑦画面カテゴリを新しく追加したとき、既存の全権限で既定が「なし」になるか（AC-12 のコード上の既定値を確認）</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>7点すべてが設計どおり</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>7点のいずれかが設計と違う状態で「画面は動くから問題なし」と判定されない</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>7点すべてが設計どおり（1つでも崩れていればNG）</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>動くかどうかではなく「そう作られているか」を見る</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>エンジニアと確認した7点の記録（画面またはコード箇所）</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>T-24_レビュー記録</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>K-01 K-02 K-03 K-04 K-05 K-06 AC-12</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>F-11 F-14 F-16 F-22</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>—（設計レビュー。顧客向けの記載なし）</t>
+        </is>
+      </c>
+      <c r="R34" s="4" t="inlineStr"/>
+      <c r="S34" s="4" t="inlineStr"/>
+      <c r="T34" s="4" t="inlineStr"/>
+      <c r="U34" s="4" t="inlineStr"/>
+      <c r="V34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35" ht="124" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>T-22</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>7シナリオの意図判定</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>これまでの結果をまとめて判定</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>T-09〜T-14 T-20</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>—（これまでの結果を集約）</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>各シナリオが意図どおり作れたかを判定</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>SC-01a/01b/02/04/06 の5件で ×（作れない）が0件</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>×（作れない）が必須5シナリオに1件でも出ない</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>SC-01a/01b/02/04/06 の5件で ×＝0件</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>SC-03・SC-05 は P1 では×が想定。判定せず記録する</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>不要（判定表に記録）</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>AC-22 AC-32</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>ケース別のやり方（6ケースすべて）</t>
+        </is>
+      </c>
+      <c r="R35" s="4" t="inlineStr"/>
+      <c r="S35" s="4" t="inlineStr"/>
+      <c r="T35" s="4" t="inlineStr"/>
+      <c r="U35" s="4" t="inlineStr"/>
+      <c r="V35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="124" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>次段階</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>T-23</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>対象外4項目の実測</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>US-05で会社情報／US-03の合計／US-02の指標／操作ログ</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>S-05 T-11／入力値：US-05／US-03／US-02／操作ログ</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>07／03_売上／09_指標の初期値</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>①US-05（閲覧のみ・区分=会社）で会社情報を変更し保存（値が更新されるか）**→確認後に元の値へ戻す** ②T-11の合計が3,000,000だったか ③US-02のダッシュボード等に出る指標を数える ④権限の作成・割当の操作ログを確認</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>判定せず実測のみ記録</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>「問題なし」と書かない。実測値をそのまま記録する</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>判定せず実測を記録（①更新可否 ②合計値 ③指標数 ④ログ有無）</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>②の合計が7,000,000なら全社が見えている＝P3が必要という判断根拠になる</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>①更新できる→P2が必要 ②700万→P3が必要 ③許可外の指標が出る→P4が必要 ④ログが無い→P5が必要</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>①会社情報の保存結果 ②US-03の合計値 ③US-02に出た指標 ④操作ログ（4枚）</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>T-23</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>AC-23 AC-24 AC-25 AC-26 AC-32</t>
+        </is>
+      </c>
+      <c r="P36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>よくあるご質問（画面は見せたいが、変更はさせたくない場合）／担当店舗を設定する（今回のリリースでは、担当店舗は割り当ての記録として保存）</t>
+        </is>
+      </c>
+      <c r="R36" s="4" t="inlineStr"/>
+      <c r="S36" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="T36" s="4" t="inlineStr"/>
+      <c r="U36" s="4" t="inlineStr"/>
+      <c r="V36" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="S3:S33">
+  <conditionalFormatting sqref="S3:S36">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -4214,7 +4490,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="S3:S33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="S3:S36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,検証不能"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -2485,22 +2485,22 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>一覧の行／一覧のマス目／役割サマリ／割当編集 の4か所から権限編集に入り、保存して着地を確認。あわせて割当編集の「＋権限を新規作成」も</t>
+          <t>一覧の行／一覧のマス目／役割サマリ／割当編集 の4か所から権限編集に入り、保存して着地を確認。あわせて割当編集の「＋権限を新規作成」も。あわせて、編集画面にベース（雛形）の選択が出ないこと、権限名を変えて保存したときの挙動を確認する</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>4入口とも保存後に来た元へ戻る。マス目からは該当箇所へ移動＋ハイライト</t>
+          <t>4入口とも保存後に来た元へ戻る。マス目からは該当箇所へ移動＋ハイライト。編集時はベース選択が出ない。権限名を変えると同じ権限の名前が変わり、その権限を持つ全員に反映される</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>入口と違う画面に着地しない。マス目から入ったときに該当箇所が開かず先頭に戻る、ということが起きない</t>
+          <t>入口と違う画面に着地しない。マス目から入ったときに該当箇所が開かず先頭に戻る、ということが起きない。権限名を変えたときに新しい権限が増える（元の権限が残ったまま2つになる）</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>4入口すべてで来た元に戻る＝4/4。マス目からの移動＋ハイライトあり</t>
+          <t>4入口すべてで来た元に戻る＝4/4。マス目からの移動＋ハイライトあり。編集時のベース選択＝非表示。名前変更後の権限数が増えない＝増加0件</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>4入口それぞれの保存後の着地画面（4枚）。マス目からはハイライトされた箇所</t>
+          <t>4入口それぞれの保存後の着地画面（4枚）。マス目からはハイライトされた箇所。編集画面にベース選択が無い状態と、名前変更後の権限一覧（権限数が増えていないこと）</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>AC-27</t>
+          <t>AC-27 AC-27 AC-38 AC-40</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>権限名の重複と区分の変更</t>
+          <t>権限名の重複・区分の変更・名前変更時の分岐</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -4141,22 +4141,22 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>既存と同じ権限名（検証_人事担当）で新規作成し保存を試みる→別名に直して保存。次に既存の権限を開いて区分を変更できるか確認する</t>
+          <t>既存と同じ権限名（検証_人事担当）で保存を試みる→別名に直して保存。次に既存の権限を開いて区分を変更できるか確認。最後に既存の権限（検証_エリア長）の名前を「検証_西エリア長」に変えて保存し、「上書き」と「新しい権限として保存」の両方を試す</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>重複した名前では保存できず「別名で保存してください」が出る。別名にすれば保存できる。既存権限の区分は変更できない</t>
+          <t>重複した名前では保存できず「別名で保存してください」が出る。既存権限の区分は変更できない。名前を変えて保存すると上書きか新規かの選択が出る。上書きなら権限数が増えず保持者が新しい名前の権限を持つ。新規なら元の権限が残り1件増える</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>同じ権限名が2つ並ぶ。区分を変更できてしまい設定値が意味を失う</t>
+          <t>同じ権限名が2つ並ぶ。区分を変更できてしまう。名前を変えたときに選択が出ずに黙って上書きされる</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>重複名での保存＝0件。別名での保存＝成功。編集時に区分が変更できる＝0件</t>
+          <t>重複名での保存＝0件。編集時に区分が変更できる＝0件。名前変更時に選択が出る＝100%。上書きで権限数の増加＝0件。新規で増加＝1件かつ元の権限が残る</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>重複名でのエラーメッセージと、編集画面で区分が変更できない状態（2枚）</t>
+          <t>重複名でのエラー、編集画面で区分が変更できない状態、名前変更時の選択ダイアログ（上書き／新しい権限として保存）の3枚</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>AC-38 AC-39</t>
+          <t>AC-38 AC-39 AC-40</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">

--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -2025,22 +2025,22 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>新規作成を開き入力項目を記録。雛形（ベース）の候補を確認。ヘッダーで新規導入デモ／運用デモを切り替える</t>
+          <t>新規作成を開き入力項目を記録。雛形（ベース）のプルダウンを開いて大カテゴリと中カテゴリを確認する。ヘッダーで新規導入デモ／運用デモを切り替える</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>雛形の候補に移植プリセットと「まっさら（なし）」が出る。運用デモでは「既存権限をコピー」が増える</t>
+          <t>ベースが スタンダードテンプレ（4種）／カスタマイズテンプレ（顧客が作った権限）／新規作成 の3カテゴリに分かれている。運用デモではカスタマイズテンプレに作成済みの権限が並ぶ</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>雛形の候補に「エリア長」が出ない（既定テンプレートではないため）</t>
+          <t>スタンダードテンプレに「エリア長」が出る（既定テンプレートではないため）</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>雛形の候補＝4種＋まっさら（なし）。エリア長は含まれない</t>
+          <t>大カテゴリ＝3つ。スタンダードテンプレ＝4種。カスタマイズテンプレ＝作成済みの権限数と一致。エリア長がスタンダードに出る＝0件</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>権限編集の基本情報。項目名（キー／ロール名／種別）と雛形プルダウンを開いた状態</t>
+          <t>ベースのプルダウンを開いた状態。3つの大カテゴリと中カテゴリが読める状態</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">

--- a/20260804_権限設定_02_検証プラン.xlsx
+++ b/20260804_権限設定_02_検証プラン.xlsx
@@ -2485,7 +2485,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>一覧の行／一覧のマス目／役割サマリ／割当編集 の4か所から権限編集に入り、保存して着地を確認。あわせて割当編集の「＋権限を新規作成」も。あわせて、編集画面にベース（雛形）の選択が出ないこと、権限名を変えて保存したときの挙動を確認する</t>
+          <t>一覧の行／一覧のマス目／役割サマリ／割当編集 の4か所から権限編集に入り、保存して着地を確認。あわせて割当編集の「＋権限を新規作成」も。あわせて、編集画面にベースの選択が出ないこと、権限名を変えて保存したときの挙動を確認する</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
